--- a/Midterm_Grades.xlsx
+++ b/Midterm_Grades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saraa\OneDrive - Emirates Schools Establishment\Attachments\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1664" documentId="13_ncr:1_{A8C90661-9620-4AA9-9960-D3F1F1731D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E105965-498C-4AF9-A8BD-5A3C2E7EEB21}"/>
+  <xr:revisionPtr revIDLastSave="1667" documentId="13_ncr:1_{A8C90661-9620-4AA9-9960-D3F1F1731D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10520715-E4EB-4159-9423-1CCD5AC69559}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1A" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="542">
   <si>
     <t>Field</t>
   </si>
@@ -777,9 +777,6 @@
     <t>يمنى سالم على العامري</t>
   </si>
   <si>
-    <t>6t</t>
-  </si>
-  <si>
     <t>ALYAZYA ALI MESFER ALI ALKHYELI</t>
   </si>
   <si>
@@ -883,9 +880,6 @@
   </si>
   <si>
     <t>Subjects</t>
-  </si>
-  <si>
-    <t>غياب ولايوجد لها درجة</t>
   </si>
   <si>
     <t>Student 21</t>
@@ -3143,52 +3137,52 @@
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>368</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>369</v>
+      </c>
+      <c r="D3" s="26" t="s">
         <v>370</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>372</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>373</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>374</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="I3" s="26" t="s">
         <v>375</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="J3" s="26" t="s">
         <v>376</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="K3" s="26" t="s">
         <v>377</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="L3" s="26" t="s">
         <v>378</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="M3" s="26" t="s">
         <v>379</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="N3" s="26" t="s">
         <v>380</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="O3" s="26" t="s">
         <v>381</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="P3" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="Q3" s="26" t="s">
         <v>383</v>
-      </c>
-      <c r="P3" s="26" t="s">
-        <v>384</v>
-      </c>
-      <c r="Q3" s="26" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="3" customFormat="1" ht="48">
@@ -3196,52 +3190,52 @@
         <v>33</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>384</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>385</v>
+      </c>
+      <c r="D4" s="26" t="s">
         <v>386</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>387</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>388</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>389</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>390</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>391</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>392</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>393</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>395</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>396</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>397</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>398</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>399</v>
-      </c>
-      <c r="P4" s="26" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q4" s="26" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="20.25">
@@ -3779,64 +3773,64 @@
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>400</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="D3" s="26" t="s">
         <v>402</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>403</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>404</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>405</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="I3" s="26" t="s">
         <v>407</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="J3" s="26" t="s">
         <v>408</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="K3" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="L3" s="26" t="s">
         <v>410</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="M3" s="26" t="s">
         <v>411</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="N3" s="26" t="s">
         <v>412</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="O3" s="26" t="s">
         <v>413</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="P3" s="26" t="s">
         <v>414</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="Q3" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="R3" s="26" t="s">
         <v>416</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="S3" s="26" t="s">
         <v>417</v>
       </c>
-      <c r="R3" s="26" t="s">
+      <c r="T3" s="26" t="s">
         <v>418</v>
       </c>
-      <c r="S3" s="26" t="s">
+      <c r="U3" s="26" t="s">
         <v>419</v>
-      </c>
-      <c r="T3" s="26" t="s">
-        <v>420</v>
-      </c>
-      <c r="U3" s="26" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="4" spans="1:21" s="3" customFormat="1" ht="48">
@@ -3844,64 +3838,64 @@
         <v>33</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="D4" s="26" t="s">
         <v>422</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>423</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>424</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>425</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>426</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>427</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>428</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>429</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>430</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>431</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>432</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>433</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>434</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>435</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="R4" s="26" t="s">
         <v>436</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="S4" s="26" t="s">
         <v>437</v>
       </c>
-      <c r="R4" s="26" t="s">
+      <c r="T4" s="26" t="s">
         <v>438</v>
       </c>
-      <c r="S4" s="26" t="s">
+      <c r="U4" s="26" t="s">
         <v>439</v>
-      </c>
-      <c r="T4" s="26" t="s">
-        <v>440</v>
-      </c>
-      <c r="U4" s="26" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="19.149999999999999">
@@ -4487,55 +4481,55 @@
         <v>17</v>
       </c>
       <c r="B3" s="73" t="s">
+        <v>440</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>441</v>
+      </c>
+      <c r="D3" s="26" t="s">
         <v>442</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>443</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>444</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>445</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>446</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="I3" s="26" t="s">
         <v>447</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="J3" s="26" t="s">
         <v>448</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="K3" s="26" t="s">
         <v>449</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="L3" s="26" t="s">
         <v>450</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="M3" s="26" t="s">
         <v>451</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="N3" s="26" t="s">
         <v>452</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="O3" s="26" t="s">
         <v>453</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="P3" s="26" t="s">
         <v>454</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="Q3" s="26" t="s">
         <v>455</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="R3" s="26" t="s">
         <v>456</v>
-      </c>
-      <c r="Q3" s="26" t="s">
-        <v>457</v>
-      </c>
-      <c r="R3" s="26" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="4" spans="1:18" s="18" customFormat="1" ht="31.5">
@@ -4543,55 +4537,55 @@
         <v>33</v>
       </c>
       <c r="B4" s="74" t="s">
+        <v>457</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>458</v>
+      </c>
+      <c r="D4" s="26" t="s">
         <v>459</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>460</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>461</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>462</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>463</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>464</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>465</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>466</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>467</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>468</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>469</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>470</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>471</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>472</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="R4" s="26" t="s">
         <v>473</v>
-      </c>
-      <c r="Q4" s="26" t="s">
-        <v>474</v>
-      </c>
-      <c r="R4" s="26" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="20.25">
@@ -5073,13 +5067,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="3" customFormat="1" ht="32.25">
@@ -5087,13 +5081,13 @@
         <v>33</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>479</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.149999999999999">
@@ -5162,7 +5156,7 @@
     </row>
     <row r="10" spans="1:4" s="1" customFormat="1" ht="18">
       <c r="A10" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B10" s="5">
         <v>85</v>
@@ -5190,7 +5184,7 @@
     </row>
     <row r="12" spans="1:4" s="1" customFormat="1" ht="18">
       <c r="A12" s="7" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B12" s="29">
         <v>94</v>
@@ -5321,43 +5315,43 @@
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>482</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>483</v>
+      </c>
+      <c r="D3" s="26" t="s">
         <v>484</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>485</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>486</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>487</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>488</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="I3" s="26" t="s">
         <v>489</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="J3" s="26" t="s">
         <v>490</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="K3" s="26" t="s">
         <v>491</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="L3" s="26" t="s">
         <v>492</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="M3" s="26" t="s">
         <v>493</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="N3" s="26" t="s">
         <v>494</v>
-      </c>
-      <c r="M3" s="26" t="s">
-        <v>495</v>
-      </c>
-      <c r="N3" s="26" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="3" customFormat="1" ht="48">
@@ -5365,43 +5359,43 @@
         <v>33</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="D4" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>498</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>499</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>500</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>501</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>502</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>503</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>504</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>505</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>506</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>507</v>
-      </c>
-      <c r="M4" s="26" t="s">
-        <v>508</v>
-      </c>
-      <c r="N4" s="26" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20.25">
@@ -5790,40 +5784,40 @@
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>508</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>509</v>
+      </c>
+      <c r="D3" s="26" t="s">
         <v>510</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>511</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>512</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>513</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>514</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="I3" s="26" t="s">
         <v>515</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="J3" s="26" t="s">
         <v>516</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="K3" s="26" t="s">
         <v>517</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="L3" s="26" t="s">
         <v>518</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="M3" s="26" t="s">
         <v>519</v>
-      </c>
-      <c r="L3" s="26" t="s">
-        <v>520</v>
-      </c>
-      <c r="M3" s="26" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="3" customFormat="1" ht="30" customHeight="1">
@@ -5831,40 +5825,40 @@
         <v>33</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>520</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>521</v>
+      </c>
+      <c r="D4" s="26" t="s">
         <v>522</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>523</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>524</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>525</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>526</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>527</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>528</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>529</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>530</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>531</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>532</v>
-      </c>
-      <c r="M4" s="26" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="18.75">
@@ -6050,7 +6044,7 @@
     </row>
     <row r="10" spans="1:13" s="1" customFormat="1" ht="18">
       <c r="A10" s="77" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B10" s="79">
         <v>64</v>
@@ -6128,7 +6122,7 @@
     </row>
     <row r="12" spans="1:13" s="1" customFormat="1" ht="18">
       <c r="A12" s="77" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B12" s="79">
         <v>80</v>
@@ -6230,19 +6224,19 @@
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>533</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>534</v>
+      </c>
+      <c r="D3" s="26" t="s">
         <v>535</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>536</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>537</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>538</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -6347,7 +6341,7 @@
     </row>
     <row r="10" spans="1:6" s="1" customFormat="1" ht="18.75">
       <c r="A10" s="47" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B10" s="89">
         <v>90</v>
@@ -6387,7 +6381,7 @@
     </row>
     <row r="12" spans="1:6" s="1" customFormat="1" ht="18.75">
       <c r="A12" s="47" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B12" s="89">
         <v>100</v>
@@ -6407,7 +6401,7 @@
     </row>
     <row r="13" spans="1:6" ht="18.75">
       <c r="A13" s="49" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B13" s="88">
         <v>100</v>
@@ -6470,10 +6464,10 @@
         <v>17</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -6481,10 +6475,10 @@
         <v>33</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="19.149999999999999">
@@ -6540,7 +6534,7 @@
     </row>
     <row r="10" spans="1:3" s="1" customFormat="1" ht="18">
       <c r="A10" s="7" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B10" s="5">
         <v>56</v>
@@ -6560,7 +6554,7 @@
     </row>
     <row r="12" spans="1:3" s="1" customFormat="1" ht="18">
       <c r="A12" s="7" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B12" s="5">
         <v>85</v>
@@ -9791,8 +9785,8 @@
       <c r="B11" s="50">
         <v>50</v>
       </c>
-      <c r="C11" s="50" t="s">
-        <v>241</v>
+      <c r="C11" s="50">
+        <v>60</v>
       </c>
       <c r="D11" s="50">
         <v>90</v>
@@ -10013,7 +10007,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="17" customFormat="1">
+    <row r="2" spans="1:18" s="17" customFormat="1" ht="15">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -10074,55 +10068,55 @@
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="D3" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="I3" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="J3" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="K3" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="L3" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="M3" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="N3" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="O3" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="P3" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="Q3" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="R3" s="26" t="s">
         <v>257</v>
-      </c>
-      <c r="R3" s="26" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:18" s="17" customFormat="1" ht="32.25">
@@ -10130,60 +10124,60 @@
         <v>33</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="R4" s="26" t="s">
         <v>274</v>
-      </c>
-      <c r="R4" s="26" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:18" s="17" customFormat="1" ht="18">
       <c r="A5" s="66" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B5" s="67"/>
       <c r="C5" s="67"/>
@@ -10213,9 +10207,7 @@
       <c r="C6" s="20">
         <v>70</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>277</v>
-      </c>
+      <c r="D6" s="20"/>
       <c r="E6" s="20">
         <v>96</v>
       </c>
@@ -10269,9 +10261,7 @@
       <c r="C7" s="12">
         <v>80</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>277</v>
-      </c>
+      <c r="D7" s="12"/>
       <c r="E7" s="12">
         <v>100</v>
       </c>
@@ -10670,24 +10660,24 @@
         <v>162</v>
       </c>
       <c r="V1" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="W1" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="X1" s="26" t="s">
         <v>278</v>
       </c>
-      <c r="W1" s="26" t="s">
+      <c r="Y1" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="X1" s="26" t="s">
+      <c r="Z1" s="26" t="s">
         <v>280</v>
-      </c>
-      <c r="Y1" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="Z1" s="26" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:26" s="17" customFormat="1" ht="15">
       <c r="A2" s="26" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B2" s="26">
         <v>1</v>
@@ -10850,79 +10840,79 @@
         <v>17</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="D4" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>285</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>289</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>291</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>294</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>295</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="R4" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="S4" s="26" t="s">
         <v>299</v>
       </c>
-      <c r="R4" s="26" t="s">
+      <c r="T4" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="S4" s="26" t="s">
+      <c r="U4" s="26" t="s">
         <v>301</v>
       </c>
-      <c r="T4" s="26" t="s">
+      <c r="V4" s="26" t="s">
         <v>302</v>
       </c>
-      <c r="U4" s="26" t="s">
+      <c r="W4" s="26" t="s">
         <v>303</v>
       </c>
-      <c r="V4" s="26" t="s">
+      <c r="X4" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="W4" s="26" t="s">
+      <c r="Y4" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="X4" s="26" t="s">
+      <c r="Z4" s="26" t="s">
         <v>306</v>
-      </c>
-      <c r="Y4" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="Z4" s="26" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:26" s="18" customFormat="1" ht="48">
@@ -10930,79 +10920,79 @@
         <v>33</v>
       </c>
       <c r="B5" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="D5" s="26" t="s">
         <v>309</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="E5" s="26" t="s">
         <v>310</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="F5" s="26" t="s">
         <v>311</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="G5" s="26" t="s">
         <v>312</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="H5" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="I5" s="26" t="s">
         <v>314</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="J5" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="I5" s="26" t="s">
+      <c r="K5" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="J5" s="26" t="s">
+      <c r="L5" s="26" t="s">
         <v>317</v>
       </c>
-      <c r="K5" s="26" t="s">
+      <c r="M5" s="26" t="s">
         <v>318</v>
       </c>
-      <c r="L5" s="26" t="s">
+      <c r="N5" s="26" t="s">
         <v>319</v>
       </c>
-      <c r="M5" s="26" t="s">
+      <c r="O5" s="26" t="s">
         <v>320</v>
       </c>
-      <c r="N5" s="26" t="s">
+      <c r="P5" s="26" t="s">
         <v>321</v>
       </c>
-      <c r="O5" s="26" t="s">
+      <c r="Q5" s="26" t="s">
         <v>322</v>
       </c>
-      <c r="P5" s="26" t="s">
+      <c r="R5" s="26" t="s">
         <v>323</v>
       </c>
-      <c r="Q5" s="26" t="s">
+      <c r="S5" s="26" t="s">
         <v>324</v>
       </c>
-      <c r="R5" s="26" t="s">
+      <c r="T5" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="S5" s="26" t="s">
+      <c r="U5" s="26" t="s">
         <v>326</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="V5" s="26" t="s">
         <v>327</v>
       </c>
-      <c r="U5" s="26" t="s">
+      <c r="W5" s="26" t="s">
         <v>328</v>
       </c>
-      <c r="V5" s="26" t="s">
+      <c r="X5" s="26" t="s">
         <v>329</v>
       </c>
-      <c r="W5" s="26" t="s">
+      <c r="Y5" s="26" t="s">
         <v>330</v>
       </c>
-      <c r="X5" s="26" t="s">
+      <c r="Z5" s="26" t="s">
         <v>331</v>
-      </c>
-      <c r="Y5" s="26" t="s">
-        <v>332</v>
-      </c>
-      <c r="Z5" s="26" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="20.25">
@@ -11669,58 +11659,58 @@
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>332</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="D3" s="26" t="s">
         <v>334</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>335</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>336</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>337</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="I3" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="J3" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="K3" s="26" t="s">
         <v>341</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="L3" s="26" t="s">
         <v>342</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="M3" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="N3" s="26" t="s">
         <v>344</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="O3" s="26" t="s">
         <v>345</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="P3" s="26" t="s">
         <v>346</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="Q3" s="26" t="s">
         <v>347</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="R3" s="26" t="s">
         <v>348</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="S3" s="26" t="s">
         <v>349</v>
-      </c>
-      <c r="R3" s="26" t="s">
-        <v>350</v>
-      </c>
-      <c r="S3" s="26" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:19" s="18" customFormat="1" ht="32.25">
@@ -11728,58 +11718,58 @@
         <v>33</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>350</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>351</v>
+      </c>
+      <c r="D4" s="26" t="s">
         <v>352</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>353</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>354</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>355</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>356</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>357</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>358</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>359</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>360</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>361</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>362</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>363</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>364</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>365</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="R4" s="26" t="s">
         <v>366</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="S4" s="26" t="s">
         <v>367</v>
-      </c>
-      <c r="R4" s="26" t="s">
-        <v>368</v>
-      </c>
-      <c r="S4" s="26" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="20.25">

--- a/Midterm_Grades.xlsx
+++ b/Midterm_Grades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saraa\OneDrive - Emirates Schools Establishment\Attachments\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1667" documentId="13_ncr:1_{A8C90661-9620-4AA9-9960-D3F1F1731D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10520715-E4EB-4159-9423-1CCD5AC69559}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA74E1B5-32AD-41F6-95B3-DD075E8F6B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1A" sheetId="1" r:id="rId1"/>
@@ -1687,7 +1687,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000\-0000\-0000000\-0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1756,6 +1756,10 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
@@ -2406,14 +2410,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" style="13" customWidth="1"/>
-    <col min="2" max="16" width="23.85546875" style="13" customWidth="1"/>
-    <col min="17" max="16384" width="8.85546875" style="13"/>
+    <col min="1" max="1" width="24.6640625" style="13" customWidth="1"/>
+    <col min="2" max="16" width="23.88671875" style="13" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
@@ -2463,7 +2467,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="58" t="s">
         <v>16</v>
       </c>
@@ -2513,7 +2517,7 @@
         <v>784202035919152</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="14" customFormat="1" ht="43.5">
+    <row r="3" spans="1:16" s="14" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>17</v>
       </c>
@@ -2563,7 +2567,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="14" customFormat="1" ht="15.75">
+    <row r="4" spans="1:16" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
@@ -2613,7 +2617,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="20.25">
+    <row r="5" spans="1:16" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
         <v>49</v>
       </c>
@@ -2633,7 +2637,7 @@
       <c r="O5" s="46"/>
       <c r="P5" s="46"/>
     </row>
-    <row r="6" spans="1:16" s="16" customFormat="1" ht="18.75">
+    <row r="6" spans="1:16" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
@@ -2683,7 +2687,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
@@ -2733,7 +2737,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="16" customFormat="1" ht="18.75">
+    <row r="8" spans="1:16" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
@@ -2783,7 +2787,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="s">
         <v>53</v>
       </c>
@@ -2833,7 +2837,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="16" customFormat="1" ht="18.75">
+    <row r="10" spans="1:16" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>54</v>
       </c>
@@ -2883,7 +2887,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="49" t="s">
         <v>55</v>
       </c>
@@ -2933,7 +2937,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
@@ -2949,7 +2953,7 @@
       <c r="O12"/>
       <c r="P12"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
@@ -2965,7 +2969,7 @@
       <c r="O13"/>
       <c r="P13"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -2981,7 +2985,7 @@
       <c r="O14"/>
       <c r="P14"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
@@ -3005,28 +3009,28 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="26.44140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="22" style="2" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="26.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.5703125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="20.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="32.44140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="26.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.88671875" style="2" customWidth="1"/>
     <col min="12" max="12" width="21" style="2" customWidth="1"/>
     <col min="13" max="13" width="22" style="2" customWidth="1"/>
-    <col min="14" max="14" width="23.85546875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="25.42578125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="25.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="25.44140625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="25.6640625" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1">
+    <row r="1" spans="1:17" s="2" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -3079,7 +3083,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="2" customFormat="1">
+    <row r="2" spans="1:17" s="2" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -3132,7 +3136,7 @@
         <v>784201451698506</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="2" customFormat="1" ht="57.75">
+    <row r="3" spans="1:17" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
@@ -3185,7 +3189,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="3" customFormat="1" ht="48">
+    <row r="4" spans="1:17" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>33</v>
       </c>
@@ -3238,7 +3242,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="20.25">
+    <row r="5" spans="1:17" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="69" t="s">
         <v>49</v>
       </c>
@@ -3259,7 +3263,7 @@
       <c r="P5" s="33"/>
       <c r="Q5" s="33"/>
     </row>
-    <row r="6" spans="1:17" s="1" customFormat="1" ht="18.75">
+    <row r="6" spans="1:17" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
@@ -3312,7 +3316,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="18.75">
+    <row r="7" spans="1:17" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
@@ -3365,7 +3369,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" ht="18.75">
+    <row r="8" spans="1:17" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
@@ -3386,7 +3390,7 @@
       <c r="P8" s="31"/>
       <c r="Q8" s="31"/>
     </row>
-    <row r="9" spans="1:17" ht="18.75">
+    <row r="9" spans="1:17" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="s">
         <v>53</v>
       </c>
@@ -3439,7 +3443,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" ht="18.75">
+    <row r="10" spans="1:17" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>54</v>
       </c>
@@ -3492,7 +3496,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="18.75">
+    <row r="11" spans="1:17" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="49" t="s">
         <v>55</v>
       </c>
@@ -3545,7 +3549,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
@@ -3560,7 +3564,7 @@
       <c r="N12"/>
       <c r="O12"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
@@ -3575,7 +3579,7 @@
       <c r="N13"/>
       <c r="O13"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -3590,7 +3594,7 @@
       <c r="N14"/>
       <c r="O14"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
@@ -3613,32 +3617,32 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:U15"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="25.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="18" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.5703125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="25.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="27.85546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="21.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.5546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="25.44140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="27.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.5546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" style="2" customWidth="1"/>
     <col min="13" max="13" width="26" style="2" customWidth="1"/>
     <col min="14" max="14" width="16" style="2" customWidth="1"/>
-    <col min="15" max="15" width="33.28515625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="33.33203125" style="2" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="22.42578125" customWidth="1"/>
-    <col min="18" max="18" width="20.28515625" customWidth="1"/>
-    <col min="19" max="19" width="12.85546875" customWidth="1"/>
-    <col min="20" max="20" width="30.7109375" customWidth="1"/>
-    <col min="21" max="21" width="30.140625" customWidth="1"/>
+    <col min="17" max="17" width="22.44140625" customWidth="1"/>
+    <col min="18" max="18" width="20.33203125" customWidth="1"/>
+    <col min="19" max="19" width="12.88671875" customWidth="1"/>
+    <col min="20" max="20" width="30.6640625" customWidth="1"/>
+    <col min="21" max="21" width="30.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1" ht="15">
+    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -3703,7 +3707,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="2" customFormat="1" ht="15">
+    <row r="2" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -3768,7 +3772,7 @@
         <v>784201336326356</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="2" customFormat="1" ht="72.75">
+    <row r="3" spans="1:21" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
@@ -3833,7 +3837,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="4" spans="1:21" s="3" customFormat="1" ht="48">
+    <row r="4" spans="1:21" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>33</v>
       </c>
@@ -3898,7 +3902,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="19.149999999999999">
+    <row r="5" spans="1:21" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="69" t="s">
         <v>49</v>
       </c>
@@ -3923,7 +3927,7 @@
       <c r="T5" s="33"/>
       <c r="U5" s="33"/>
     </row>
-    <row r="6" spans="1:21" s="1" customFormat="1" ht="18.75">
+    <row r="6" spans="1:21" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
@@ -3988,7 +3992,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="18.75">
+    <row r="7" spans="1:21" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
@@ -4053,7 +4057,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:21" s="1" customFormat="1" ht="18">
+    <row r="8" spans="1:21" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
@@ -4118,7 +4122,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="18">
+    <row r="9" spans="1:21" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="s">
         <v>53</v>
       </c>
@@ -4143,7 +4147,7 @@
       <c r="T9" s="28"/>
       <c r="U9" s="28"/>
     </row>
-    <row r="10" spans="1:21" s="1" customFormat="1" ht="18">
+    <row r="10" spans="1:21" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>54</v>
       </c>
@@ -4208,7 +4212,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="18">
+    <row r="11" spans="1:21" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="49" t="s">
         <v>55</v>
       </c>
@@ -4273,7 +4277,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
@@ -4288,7 +4292,7 @@
       <c r="N12"/>
       <c r="O12"/>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
@@ -4303,7 +4307,7 @@
       <c r="N13"/>
       <c r="O13"/>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -4318,7 +4322,7 @@
       <c r="N14"/>
       <c r="O14"/>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
@@ -4341,30 +4345,30 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" style="17" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" style="17" customWidth="1"/>
     <col min="2" max="2" width="21" style="17" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" style="17" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" style="17" customWidth="1"/>
-    <col min="7" max="7" width="28.140625" style="17" customWidth="1"/>
-    <col min="8" max="8" width="24.140625" style="17" customWidth="1"/>
-    <col min="9" max="9" width="30.28515625" style="17" customWidth="1"/>
-    <col min="10" max="10" width="21.28515625" style="17" customWidth="1"/>
-    <col min="11" max="11" width="34.28515625" style="17" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" style="17" customWidth="1"/>
-    <col min="13" max="13" width="27.7109375" style="17" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" style="17" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" style="17" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" style="17" customWidth="1"/>
+    <col min="7" max="7" width="28.109375" style="17" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" style="17" customWidth="1"/>
+    <col min="9" max="9" width="30.33203125" style="17" customWidth="1"/>
+    <col min="10" max="10" width="21.33203125" style="17" customWidth="1"/>
+    <col min="11" max="11" width="34.33203125" style="17" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" style="17" customWidth="1"/>
+    <col min="13" max="13" width="27.6640625" style="17" customWidth="1"/>
     <col min="14" max="14" width="28" style="17" customWidth="1"/>
-    <col min="15" max="15" width="23.140625" style="17" customWidth="1"/>
-    <col min="16" max="16" width="34.42578125" style="17" customWidth="1"/>
-    <col min="17" max="17" width="32.85546875" style="17" customWidth="1"/>
-    <col min="18" max="18" width="20.7109375" style="17" customWidth="1"/>
-    <col min="19" max="16384" width="8.85546875" style="13"/>
+    <col min="15" max="15" width="23.109375" style="17" customWidth="1"/>
+    <col min="16" max="16" width="34.44140625" style="17" customWidth="1"/>
+    <col min="17" max="17" width="32.88671875" style="17" customWidth="1"/>
+    <col min="18" max="18" width="20.6640625" style="17" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="17" customFormat="1" ht="15">
+    <row r="1" spans="1:18" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -4420,7 +4424,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="17" customFormat="1" ht="15">
+    <row r="2" spans="1:18" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -4476,7 +4480,7 @@
         <v>784201292650468</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="17" customFormat="1" ht="57.75">
+    <row r="3" spans="1:18" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
@@ -4532,7 +4536,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="18" customFormat="1" ht="31.5">
+    <row r="4" spans="1:18" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>33</v>
       </c>
@@ -4588,7 +4592,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.25">
+    <row r="5" spans="1:18" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
         <v>49</v>
       </c>
@@ -4610,7 +4614,7 @@
       <c r="Q5" s="45"/>
       <c r="R5" s="45"/>
     </row>
-    <row r="6" spans="1:18" s="16" customFormat="1" ht="18.75">
+    <row r="6" spans="1:18" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
@@ -4666,7 +4670,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="18.75">
+    <row r="7" spans="1:18" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
@@ -4722,7 +4726,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="16" customFormat="1" ht="18.75">
+    <row r="8" spans="1:18" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
@@ -4778,7 +4782,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="18.75">
+    <row r="9" spans="1:18" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="s">
         <v>53</v>
       </c>
@@ -4834,7 +4838,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="16" customFormat="1" ht="18.75">
+    <row r="10" spans="1:18" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>54</v>
       </c>
@@ -4890,7 +4894,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="18.75">
+    <row r="11" spans="1:18" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="49" t="s">
         <v>55</v>
       </c>
@@ -4946,7 +4950,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
@@ -4964,7 +4968,7 @@
       <c r="Q12"/>
       <c r="R12"/>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
@@ -4982,7 +4986,7 @@
       <c r="Q13"/>
       <c r="R13"/>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -5000,7 +5004,7 @@
       <c r="Q14"/>
       <c r="R14"/>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
@@ -5026,15 +5030,15 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" style="2" customWidth="1"/>
     <col min="2" max="2" width="41" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" ht="15">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5048,7 +5052,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="2" customFormat="1" ht="15">
+    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>16</v>
       </c>
@@ -5062,7 +5066,7 @@
         <v>784201175424163</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" ht="43.5">
+    <row r="3" spans="1:4" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>17</v>
       </c>
@@ -5076,7 +5080,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="3" customFormat="1" ht="32.25">
+    <row r="4" spans="1:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>33</v>
       </c>
@@ -5090,7 +5094,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="19.149999999999999">
+    <row r="5" spans="1:4" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>49</v>
       </c>
@@ -5098,7 +5102,7 @@
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
     </row>
-    <row r="6" spans="1:4" s="1" customFormat="1" ht="18">
+    <row r="6" spans="1:4" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>50</v>
       </c>
@@ -5112,7 +5116,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18">
+    <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>51</v>
       </c>
@@ -5126,7 +5130,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="1" customFormat="1" ht="18">
+    <row r="8" spans="1:4" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>52</v>
       </c>
@@ -5140,7 +5144,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18">
+    <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>53</v>
       </c>
@@ -5154,7 +5158,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="1" customFormat="1" ht="18">
+    <row r="10" spans="1:4" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>480</v>
       </c>
@@ -5168,7 +5172,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18">
+    <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
@@ -5182,7 +5186,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="1" customFormat="1" ht="18">
+    <row r="12" spans="1:4" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>481</v>
       </c>
@@ -5204,25 +5208,25 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" customWidth="1"/>
-    <col min="12" max="12" width="22.140625" customWidth="1"/>
-    <col min="13" max="13" width="22.28515625" customWidth="1"/>
-    <col min="14" max="14" width="32.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" customWidth="1"/>
+    <col min="11" max="11" width="19.44140625" customWidth="1"/>
+    <col min="12" max="12" width="22.109375" customWidth="1"/>
+    <col min="13" max="13" width="22.33203125" customWidth="1"/>
+    <col min="14" max="14" width="32.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -5266,7 +5270,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="2" customFormat="1">
+    <row r="2" spans="1:14" s="2" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -5310,7 +5314,7 @@
         <v>784201182506283</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="2" customFormat="1" ht="57.75">
+    <row r="3" spans="1:14" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
@@ -5354,7 +5358,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="3" customFormat="1" ht="48">
+    <row r="4" spans="1:14" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>33</v>
       </c>
@@ -5398,7 +5402,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="20.25">
+    <row r="5" spans="1:14" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
         <v>49</v>
       </c>
@@ -5416,7 +5420,7 @@
       <c r="M5" s="46"/>
       <c r="N5" s="46"/>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="18.75">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
@@ -5458,7 +5462,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="18.75">
+    <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
@@ -5502,7 +5506,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="18.75">
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
@@ -5546,7 +5550,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="18.75">
+    <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="s">
         <v>53</v>
       </c>
@@ -5590,7 +5594,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="18.75">
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>54</v>
       </c>
@@ -5628,7 +5632,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="18.75">
+    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="49" t="s">
         <v>55</v>
       </c>
@@ -5680,24 +5684,24 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.109375" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
-    <col min="5" max="5" width="32.85546875" customWidth="1"/>
-    <col min="6" max="6" width="25.28515625" customWidth="1"/>
-    <col min="7" max="7" width="27.7109375" customWidth="1"/>
-    <col min="8" max="8" width="24.28515625" customWidth="1"/>
-    <col min="9" max="9" width="34.140625" customWidth="1"/>
-    <col min="10" max="10" width="27.42578125" customWidth="1"/>
-    <col min="11" max="11" width="34.28515625" customWidth="1"/>
-    <col min="12" max="12" width="20.140625" customWidth="1"/>
-    <col min="13" max="13" width="31.85546875" customWidth="1"/>
+    <col min="5" max="5" width="32.88671875" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" customWidth="1"/>
+    <col min="7" max="7" width="27.6640625" customWidth="1"/>
+    <col min="8" max="8" width="24.33203125" customWidth="1"/>
+    <col min="9" max="9" width="34.109375" customWidth="1"/>
+    <col min="10" max="10" width="27.44140625" customWidth="1"/>
+    <col min="11" max="11" width="34.33203125" customWidth="1"/>
+    <col min="12" max="12" width="20.109375" customWidth="1"/>
+    <col min="13" max="13" width="31.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="15">
+    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -5738,7 +5742,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="2" customFormat="1" ht="15">
+    <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -5779,7 +5783,7 @@
         <v>784201074839693</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" ht="34.5" customHeight="1">
+    <row r="3" spans="1:13" s="2" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
@@ -5820,7 +5824,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="3" customFormat="1" ht="30" customHeight="1">
+    <row r="4" spans="1:13" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>33</v>
       </c>
@@ -5861,7 +5865,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18.75">
+    <row r="5" spans="1:13" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="76" t="s">
         <v>49</v>
       </c>
@@ -5878,7 +5882,7 @@
       <c r="L5" s="67"/>
       <c r="M5" s="67"/>
     </row>
-    <row r="6" spans="1:13" s="1" customFormat="1" ht="18">
+    <row r="6" spans="1:13" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="77" t="s">
         <v>50</v>
       </c>
@@ -5919,7 +5923,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18">
+    <row r="7" spans="1:13" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="78" t="s">
         <v>51</v>
       </c>
@@ -5960,7 +5964,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="1" customFormat="1" ht="18">
+    <row r="8" spans="1:13" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="77" t="s">
         <v>52</v>
       </c>
@@ -6001,7 +6005,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="18">
+    <row r="9" spans="1:13" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="78" t="s">
         <v>53</v>
       </c>
@@ -6042,7 +6046,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="1" customFormat="1" ht="18">
+    <row r="10" spans="1:13" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="77" t="s">
         <v>532</v>
       </c>
@@ -6079,7 +6083,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="18">
+    <row r="11" spans="1:13" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="78" t="s">
         <v>55</v>
       </c>
@@ -6120,7 +6124,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="1" customFormat="1" ht="18">
+    <row r="12" spans="1:13" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="77" t="s">
         <v>481</v>
       </c>
@@ -6169,17 +6173,17 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" style="24" customWidth="1"/>
-    <col min="3" max="3" width="31.42578125" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.85546875" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" style="24" customWidth="1"/>
+    <col min="3" max="3" width="31.44140625" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" customWidth="1"/>
+    <col min="6" max="6" width="22.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1">
+    <row r="1" spans="1:6" s="2" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -6199,7 +6203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" ht="15.75">
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -6219,7 +6223,7 @@
         <v>784200938542402</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" ht="60" customHeight="1">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
@@ -6239,7 +6243,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="4" spans="1:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>33</v>
       </c>
@@ -6249,7 +6253,7 @@
       <c r="E4" s="68"/>
       <c r="F4" s="68"/>
     </row>
-    <row r="5" spans="1:6" ht="20.25">
+    <row r="5" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="69" t="s">
         <v>49</v>
       </c>
@@ -6259,7 +6263,7 @@
       <c r="E5" s="82"/>
       <c r="F5" s="82"/>
     </row>
-    <row r="6" spans="1:6" s="1" customFormat="1" ht="18.75">
+    <row r="6" spans="1:6" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
@@ -6279,7 +6283,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18.75">
+    <row r="7" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
@@ -6299,7 +6303,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="1" customFormat="1" ht="18.75">
+    <row r="8" spans="1:6" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
@@ -6319,7 +6323,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="18.75">
+    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="s">
         <v>53</v>
       </c>
@@ -6339,7 +6343,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="1" customFormat="1" ht="18.75">
+    <row r="10" spans="1:6" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>480</v>
       </c>
@@ -6359,7 +6363,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="18.75">
+    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="49" t="s">
         <v>55</v>
       </c>
@@ -6379,7 +6383,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="1" customFormat="1" ht="18.75">
+    <row r="12" spans="1:6" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
         <v>481</v>
       </c>
@@ -6399,7 +6403,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="18.75">
+    <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="49" t="s">
         <v>532</v>
       </c>
@@ -6419,7 +6423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18.75">
+    <row r="14" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="23"/>
     </row>
   </sheetData>
@@ -6430,14 +6434,14 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
-    <col min="3" max="3" width="26.5703125" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" customWidth="1"/>
+    <col min="3" max="3" width="26.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -6448,7 +6452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" ht="15">
+    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>16</v>
       </c>
@@ -6459,7 +6463,7 @@
         <v>784200870976030</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="2" customFormat="1" ht="51" customHeight="1">
+    <row r="3" spans="1:3" s="2" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>17</v>
       </c>
@@ -6470,7 +6474,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="4" spans="1:3" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>33</v>
       </c>
@@ -6481,14 +6485,14 @@
         <v>541</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="19.149999999999999">
+    <row r="5" spans="1:3" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>49</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
     </row>
-    <row r="6" spans="1:3" s="1" customFormat="1" ht="18">
+    <row r="6" spans="1:3" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>50</v>
       </c>
@@ -6499,7 +6503,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18">
+    <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>51</v>
       </c>
@@ -6510,7 +6514,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="1" customFormat="1" ht="18">
+    <row r="8" spans="1:3" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>52</v>
       </c>
@@ -6521,7 +6525,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18.75">
+    <row r="9" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>53</v>
       </c>
@@ -6532,7 +6536,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="1" customFormat="1" ht="18">
+    <row r="10" spans="1:3" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>532</v>
       </c>
@@ -6543,7 +6547,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18">
+    <row r="11" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
@@ -6552,7 +6556,7 @@
       </c>
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:3" s="1" customFormat="1" ht="18">
+    <row r="12" spans="1:3" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>481</v>
       </c>
@@ -6571,15 +6575,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" style="17" customWidth="1"/>
-    <col min="2" max="16" width="22.140625" style="17" customWidth="1"/>
-    <col min="17" max="17" width="22.140625" style="13" customWidth="1"/>
-    <col min="18" max="16384" width="8.85546875" style="13"/>
+    <col min="1" max="1" width="25.88671875" style="17" customWidth="1"/>
+    <col min="2" max="16" width="22.109375" style="17" customWidth="1"/>
+    <col min="17" max="17" width="22.109375" style="13" customWidth="1"/>
+    <col min="18" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="17" customFormat="1" ht="15">
+    <row r="1" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -6632,7 +6636,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="17" customFormat="1" ht="15">
+    <row r="2" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -6685,7 +6689,7 @@
         <v>784202052052143</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="17" customFormat="1" ht="35.25">
+    <row r="3" spans="1:17" s="17" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
@@ -6738,7 +6742,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="18" customFormat="1" ht="15.75">
+    <row r="4" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>33</v>
       </c>
@@ -6791,7 +6795,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="20.25">
+    <row r="5" spans="1:17" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
         <v>49</v>
       </c>
@@ -6812,7 +6816,7 @@
       <c r="P5" s="45"/>
       <c r="Q5" s="59"/>
     </row>
-    <row r="6" spans="1:17" s="16" customFormat="1" ht="18">
+    <row r="6" spans="1:17" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
@@ -6865,7 +6869,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="18">
+    <row r="7" spans="1:17" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
@@ -6918,7 +6922,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="16" customFormat="1" ht="18">
+    <row r="8" spans="1:17" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
@@ -6971,7 +6975,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="18.75">
+    <row r="9" spans="1:17" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="s">
         <v>53</v>
       </c>
@@ -7024,7 +7028,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="16" customFormat="1" ht="18.75">
+    <row r="10" spans="1:17" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>54</v>
       </c>
@@ -7077,7 +7081,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="18.75">
+    <row r="11" spans="1:17" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="49" t="s">
         <v>55</v>
       </c>
@@ -7130,7 +7134,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
@@ -7147,7 +7151,7 @@
       <c r="P12"/>
       <c r="Q12"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
@@ -7164,7 +7168,7 @@
       <c r="P13"/>
       <c r="Q13"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -7181,7 +7185,7 @@
       <c r="P14"/>
       <c r="Q14"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
@@ -7206,29 +7210,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" style="17" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="17" customWidth="1"/>
-    <col min="4" max="5" width="15.85546875" style="17" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="17" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="17" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" style="17" customWidth="1"/>
-    <col min="9" max="10" width="16.28515625" style="17" customWidth="1"/>
-    <col min="11" max="11" width="19.5703125" style="17" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" style="17" customWidth="1"/>
+    <col min="4" max="5" width="15.88671875" style="17" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" style="17" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" style="17" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" style="17" customWidth="1"/>
+    <col min="9" max="10" width="16.33203125" style="17" customWidth="1"/>
+    <col min="11" max="11" width="19.5546875" style="17" customWidth="1"/>
     <col min="12" max="12" width="16" style="17" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" style="17" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="17" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" style="17" customWidth="1"/>
-    <col min="16" max="16" width="15.7109375" style="17" customWidth="1"/>
-    <col min="17" max="17" width="16.140625" style="22" customWidth="1"/>
-    <col min="18" max="18" width="15.7109375" style="22" customWidth="1"/>
-    <col min="19" max="19" width="16.28515625" style="22" customWidth="1"/>
-    <col min="20" max="16384" width="8.85546875" style="13"/>
+    <col min="13" max="13" width="18.33203125" style="17" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" style="17" customWidth="1"/>
+    <col min="15" max="15" width="16.109375" style="17" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" style="17" customWidth="1"/>
+    <col min="17" max="17" width="16.109375" style="22" customWidth="1"/>
+    <col min="18" max="18" width="15.6640625" style="22" customWidth="1"/>
+    <col min="19" max="19" width="16.33203125" style="22" customWidth="1"/>
+    <col min="20" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -7287,7 +7291,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -7346,7 +7350,7 @@
         <v>784201991531654</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="72">
+    <row r="3" spans="1:19" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
@@ -7405,7 +7409,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="21" customFormat="1" ht="48">
+    <row r="4" spans="1:19" s="21" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>33</v>
       </c>
@@ -7464,7 +7468,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="19.149999999999999">
+    <row r="5" spans="1:19" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
         <v>49</v>
       </c>
@@ -7487,7 +7491,7 @@
       <c r="R5" s="55"/>
       <c r="S5" s="55"/>
     </row>
-    <row r="6" spans="1:19" s="16" customFormat="1" ht="18">
+    <row r="6" spans="1:19" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
@@ -7546,7 +7550,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="18">
+    <row r="7" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
@@ -7605,7 +7609,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="16" customFormat="1" ht="18">
+    <row r="8" spans="1:19" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
@@ -7662,7 +7666,7 @@
       </c>
       <c r="S8" s="56"/>
     </row>
-    <row r="9" spans="1:19" ht="18">
+    <row r="9" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="s">
         <v>53</v>
       </c>
@@ -7721,7 +7725,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="16" customFormat="1" ht="18">
+    <row r="10" spans="1:19" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>54</v>
       </c>
@@ -7744,7 +7748,7 @@
       <c r="R10" s="56"/>
       <c r="S10" s="56"/>
     </row>
-    <row r="11" spans="1:19" ht="18">
+    <row r="11" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="49" t="s">
         <v>55</v>
       </c>
@@ -7803,7 +7807,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
@@ -7822,7 +7826,7 @@
       <c r="R12"/>
       <c r="S12"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
@@ -7841,7 +7845,7 @@
       <c r="R13"/>
       <c r="S13"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -7860,7 +7864,7 @@
       <c r="R14"/>
       <c r="S14"/>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
@@ -7887,30 +7891,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.140625" style="17" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="17" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" style="17" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" style="17" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" style="17" customWidth="1"/>
-    <col min="6" max="6" width="26.28515625" style="17" customWidth="1"/>
-    <col min="7" max="7" width="21.140625" style="17" customWidth="1"/>
-    <col min="8" max="8" width="30.85546875" style="17" customWidth="1"/>
-    <col min="9" max="9" width="21.140625" style="17" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="17" customWidth="1"/>
-    <col min="11" max="11" width="21.140625" style="17" customWidth="1"/>
-    <col min="12" max="12" width="29.140625" style="17" customWidth="1"/>
-    <col min="13" max="13" width="22.140625" style="17" customWidth="1"/>
-    <col min="14" max="14" width="21.28515625" style="17" customWidth="1"/>
-    <col min="15" max="15" width="22.42578125" style="17" customWidth="1"/>
-    <col min="16" max="16" width="24.140625" style="17" customWidth="1"/>
-    <col min="17" max="17" width="21.42578125" style="13" customWidth="1"/>
+    <col min="1" max="1" width="30.109375" style="17" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="17" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" style="17" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" style="17" customWidth="1"/>
+    <col min="6" max="6" width="26.33203125" style="17" customWidth="1"/>
+    <col min="7" max="7" width="21.109375" style="17" customWidth="1"/>
+    <col min="8" max="8" width="30.88671875" style="17" customWidth="1"/>
+    <col min="9" max="9" width="21.109375" style="17" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" style="17" customWidth="1"/>
+    <col min="11" max="11" width="21.109375" style="17" customWidth="1"/>
+    <col min="12" max="12" width="29.109375" style="17" customWidth="1"/>
+    <col min="13" max="13" width="22.109375" style="17" customWidth="1"/>
+    <col min="14" max="14" width="21.33203125" style="17" customWidth="1"/>
+    <col min="15" max="15" width="22.44140625" style="17" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" style="17" customWidth="1"/>
+    <col min="17" max="17" width="21.44140625" style="13" customWidth="1"/>
     <col min="18" max="18" width="26" style="13" customWidth="1"/>
-    <col min="19" max="16384" width="8.85546875" style="13"/>
+    <col min="19" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="17" customFormat="1">
+    <row r="1" spans="1:18" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -7966,7 +7970,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="17" customFormat="1">
+    <row r="2" spans="1:18" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -8022,7 +8026,7 @@
         <v>784201920696156</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="17" customFormat="1" ht="57.6">
+    <row r="3" spans="1:18" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
@@ -8078,7 +8082,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="18" customFormat="1" ht="32.25">
+    <row r="4" spans="1:18" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>33</v>
       </c>
@@ -8134,7 +8138,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="19.149999999999999">
+    <row r="5" spans="1:18" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
         <v>49</v>
       </c>
@@ -8156,7 +8160,7 @@
       <c r="Q5" s="46"/>
       <c r="R5" s="46"/>
     </row>
-    <row r="6" spans="1:18" s="16" customFormat="1" ht="18">
+    <row r="6" spans="1:18" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
@@ -8212,7 +8216,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="18">
+    <row r="7" spans="1:18" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
@@ -8268,7 +8272,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="16" customFormat="1" ht="18">
+    <row r="8" spans="1:18" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
@@ -8324,7 +8328,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="18">
+    <row r="9" spans="1:18" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="s">
         <v>53</v>
       </c>
@@ -8380,7 +8384,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="16" customFormat="1" ht="18">
+    <row r="10" spans="1:18" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>54</v>
       </c>
@@ -8402,7 +8406,7 @@
       <c r="Q10" s="48"/>
       <c r="R10" s="48"/>
     </row>
-    <row r="11" spans="1:18" ht="18">
+    <row r="11" spans="1:18" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="52" t="s">
         <v>55</v>
       </c>
@@ -8458,7 +8462,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
@@ -8476,7 +8480,7 @@
       <c r="Q12"/>
       <c r="R12"/>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
@@ -8494,7 +8498,7 @@
       <c r="Q13"/>
       <c r="R13"/>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -8512,7 +8516,7 @@
       <c r="Q14"/>
       <c r="R14"/>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
@@ -8538,33 +8542,33 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:U15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" style="17" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="29.140625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" style="17" customWidth="1"/>
-    <col min="6" max="6" width="32.28515625" style="17" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="29.109375" style="17" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" style="17" customWidth="1"/>
+    <col min="6" max="6" width="32.33203125" style="17" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" style="17" customWidth="1"/>
     <col min="8" max="8" width="39" style="17" customWidth="1"/>
     <col min="9" max="9" width="34" style="17" customWidth="1"/>
-    <col min="10" max="10" width="30.7109375" style="17" customWidth="1"/>
-    <col min="11" max="11" width="37.7109375" style="17" customWidth="1"/>
-    <col min="12" max="12" width="44.5703125" style="17" customWidth="1"/>
-    <col min="13" max="13" width="35.7109375" style="17" customWidth="1"/>
-    <col min="14" max="14" width="27.5703125" style="17" customWidth="1"/>
-    <col min="15" max="15" width="27.7109375" style="17" customWidth="1"/>
+    <col min="10" max="10" width="30.6640625" style="17" customWidth="1"/>
+    <col min="11" max="11" width="37.6640625" style="17" customWidth="1"/>
+    <col min="12" max="12" width="44.5546875" style="17" customWidth="1"/>
+    <col min="13" max="13" width="35.6640625" style="17" customWidth="1"/>
+    <col min="14" max="14" width="27.5546875" style="17" customWidth="1"/>
+    <col min="15" max="15" width="27.6640625" style="17" customWidth="1"/>
     <col min="16" max="16" width="28" style="13" customWidth="1"/>
     <col min="17" max="17" width="19" style="13" customWidth="1"/>
-    <col min="18" max="18" width="21.140625" style="13" customWidth="1"/>
+    <col min="18" max="18" width="21.109375" style="13" customWidth="1"/>
     <col min="19" max="19" width="20" style="13" customWidth="1"/>
-    <col min="20" max="20" width="21.5703125" style="13" customWidth="1"/>
-    <col min="21" max="21" width="21.7109375" style="13" customWidth="1"/>
-    <col min="22" max="16384" width="8.85546875" style="13"/>
+    <col min="20" max="20" width="21.5546875" style="13" customWidth="1"/>
+    <col min="21" max="21" width="21.6640625" style="13" customWidth="1"/>
+    <col min="22" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="17" customFormat="1" ht="15">
+    <row r="1" spans="1:21" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -8629,7 +8633,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="17" customFormat="1" ht="15">
+    <row r="2" spans="1:21" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -8694,7 +8698,7 @@
         <v>784201820864300</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="17" customFormat="1" ht="57.75">
+    <row r="3" spans="1:21" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
@@ -8759,7 +8763,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="4" spans="1:21" s="18" customFormat="1" ht="32.25">
+    <row r="4" spans="1:21" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>33</v>
       </c>
@@ -8824,7 +8828,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="20.25">
+    <row r="5" spans="1:21" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>49</v>
       </c>
@@ -8849,7 +8853,7 @@
       <c r="T5" s="34"/>
       <c r="U5" s="43"/>
     </row>
-    <row r="6" spans="1:21" s="16" customFormat="1" ht="18.75">
+    <row r="6" spans="1:21" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>50</v>
       </c>
@@ -8914,7 +8918,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="18.75">
+    <row r="7" spans="1:21" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>51</v>
       </c>
@@ -8979,7 +8983,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:21" s="16" customFormat="1" ht="18.75">
+    <row r="8" spans="1:21" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>52</v>
       </c>
@@ -9004,7 +9008,7 @@
       <c r="T8" s="35"/>
       <c r="U8" s="39"/>
     </row>
-    <row r="9" spans="1:21" ht="18.75">
+    <row r="9" spans="1:21" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>53</v>
       </c>
@@ -9029,7 +9033,7 @@
       <c r="T9" s="40"/>
       <c r="U9" s="42"/>
     </row>
-    <row r="10" spans="1:21" s="16" customFormat="1" ht="18.75">
+    <row r="10" spans="1:21" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>54</v>
       </c>
@@ -9094,7 +9098,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="18.75">
+    <row r="11" spans="1:21" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
@@ -9157,7 +9161,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
@@ -9178,7 +9182,7 @@
       <c r="T12"/>
       <c r="U12"/>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
@@ -9199,7 +9203,7 @@
       <c r="T13"/>
       <c r="U13"/>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -9220,7 +9224,7 @@
       <c r="T14"/>
       <c r="U14"/>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
@@ -9249,32 +9253,32 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:T15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.42578125" style="17" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" style="17" customWidth="1"/>
-    <col min="6" max="6" width="29.28515625" style="17" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" style="17" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" style="17" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" style="17" customWidth="1"/>
-    <col min="10" max="10" width="30.28515625" style="17" customWidth="1"/>
+    <col min="1" max="1" width="47.44140625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" style="17" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" style="17" customWidth="1"/>
+    <col min="6" max="6" width="29.33203125" style="17" customWidth="1"/>
+    <col min="7" max="7" width="22.88671875" style="17" customWidth="1"/>
+    <col min="8" max="8" width="25.109375" style="17" customWidth="1"/>
+    <col min="9" max="9" width="17.5546875" style="17" customWidth="1"/>
+    <col min="10" max="10" width="30.33203125" style="17" customWidth="1"/>
     <col min="11" max="11" width="23" style="17" customWidth="1"/>
-    <col min="12" max="12" width="25.28515625" style="17" customWidth="1"/>
-    <col min="13" max="13" width="23.28515625" style="17" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" style="17" customWidth="1"/>
-    <col min="15" max="15" width="29.7109375" style="17" customWidth="1"/>
-    <col min="16" max="16" width="25.140625" style="13" customWidth="1"/>
-    <col min="17" max="17" width="23.28515625" style="13" customWidth="1"/>
-    <col min="18" max="18" width="23.5703125" style="13" customWidth="1"/>
+    <col min="12" max="12" width="25.33203125" style="17" customWidth="1"/>
+    <col min="13" max="13" width="23.33203125" style="17" customWidth="1"/>
+    <col min="14" max="14" width="15.88671875" style="17" customWidth="1"/>
+    <col min="15" max="15" width="29.6640625" style="17" customWidth="1"/>
+    <col min="16" max="16" width="25.109375" style="13" customWidth="1"/>
+    <col min="17" max="17" width="23.33203125" style="13" customWidth="1"/>
+    <col min="18" max="18" width="23.5546875" style="13" customWidth="1"/>
     <col min="19" max="19" width="29" style="13" customWidth="1"/>
-    <col min="20" max="20" width="38.140625" style="13" customWidth="1"/>
-    <col min="21" max="16384" width="8.85546875" style="13"/>
+    <col min="20" max="20" width="38.109375" style="13" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="17" customFormat="1" ht="15">
+    <row r="1" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -9336,7 +9340,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="17" customFormat="1" ht="15">
+    <row r="2" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -9398,7 +9402,7 @@
         <v>784201728706827</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="17" customFormat="1" ht="57.75">
+    <row r="3" spans="1:20" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
@@ -9460,7 +9464,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" spans="1:20" s="18" customFormat="1" ht="32.25">
+    <row r="4" spans="1:20" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>33</v>
       </c>
@@ -9522,7 +9526,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="20.25">
+    <row r="5" spans="1:20" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
         <v>49</v>
       </c>
@@ -9546,7 +9550,7 @@
       <c r="S5" s="60"/>
       <c r="T5" s="45"/>
     </row>
-    <row r="6" spans="1:20" s="16" customFormat="1" ht="18.75">
+    <row r="6" spans="1:20" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
@@ -9608,7 +9612,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="18">
+    <row r="7" spans="1:20" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
@@ -9668,7 +9672,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:20" s="16" customFormat="1" ht="18.75">
+    <row r="8" spans="1:20" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
@@ -9692,7 +9696,7 @@
       <c r="S8" s="61"/>
       <c r="T8" s="39"/>
     </row>
-    <row r="9" spans="1:20" ht="18">
+    <row r="9" spans="1:20" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="s">
         <v>53</v>
       </c>
@@ -9716,7 +9720,7 @@
       <c r="S9" s="32"/>
       <c r="T9" s="28"/>
     </row>
-    <row r="10" spans="1:20" s="16" customFormat="1" ht="18.75">
+    <row r="10" spans="1:20" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>54</v>
       </c>
@@ -9778,7 +9782,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="18">
+    <row r="11" spans="1:20" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="49" t="s">
         <v>55</v>
       </c>
@@ -9840,7 +9844,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
@@ -9860,7 +9864,7 @@
       <c r="S12"/>
       <c r="T12"/>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
@@ -9880,7 +9884,7 @@
       <c r="S13"/>
       <c r="T13"/>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -9900,7 +9904,7 @@
       <c r="S14"/>
       <c r="T14"/>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
@@ -9927,31 +9931,31 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:R16"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <dimension ref="A1:R17"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.42578125" style="17" customWidth="1"/>
-    <col min="2" max="2" width="34.28515625" style="17" customWidth="1"/>
-    <col min="3" max="3" width="36.28515625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" style="17" customWidth="1"/>
+    <col min="1" max="1" width="34.44140625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="34.33203125" style="17" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" style="17" customWidth="1"/>
     <col min="6" max="6" width="23" style="17" customWidth="1"/>
-    <col min="7" max="7" width="23.85546875" style="17" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" style="17" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" style="17" customWidth="1"/>
-    <col min="10" max="10" width="27.140625" style="17" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" style="17" customWidth="1"/>
-    <col min="12" max="12" width="22.42578125" style="17" customWidth="1"/>
+    <col min="7" max="7" width="23.88671875" style="17" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" style="17" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" style="17" customWidth="1"/>
+    <col min="10" max="10" width="27.109375" style="17" customWidth="1"/>
+    <col min="11" max="11" width="20.6640625" style="17" customWidth="1"/>
+    <col min="12" max="12" width="22.44140625" style="17" customWidth="1"/>
     <col min="13" max="13" width="34" style="17" customWidth="1"/>
-    <col min="14" max="14" width="24.28515625" style="17" customWidth="1"/>
-    <col min="15" max="15" width="30.42578125" style="17" customWidth="1"/>
-    <col min="16" max="16" width="29.42578125" style="13" customWidth="1"/>
-    <col min="17" max="17" width="29.5703125" style="13" customWidth="1"/>
-    <col min="18" max="18" width="22.140625" style="13" customWidth="1"/>
-    <col min="19" max="16384" width="8.85546875" style="13"/>
+    <col min="14" max="14" width="24.33203125" style="17" customWidth="1"/>
+    <col min="15" max="15" width="30.44140625" style="17" customWidth="1"/>
+    <col min="16" max="16" width="29.44140625" style="13" customWidth="1"/>
+    <col min="17" max="17" width="29.5546875" style="13" customWidth="1"/>
+    <col min="18" max="18" width="22.109375" style="13" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="17" customFormat="1">
+    <row r="1" spans="1:18" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -10007,499 +10011,501 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="17" customFormat="1" ht="15">
-      <c r="A2" s="26" t="s">
+    <row r="2" spans="1:18" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26"/>
+      <c r="B2" s="26">
+        <v>1</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+    </row>
+    <row r="3" spans="1:18" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="38">
+      <c r="B3" s="38">
         <v>784201770479307</v>
       </c>
-      <c r="C2" s="38">
+      <c r="C3" s="38">
         <v>784201743743987</v>
       </c>
-      <c r="D2" s="38">
+      <c r="D3" s="38">
         <v>784201625962713</v>
       </c>
-      <c r="E2" s="38">
+      <c r="E3" s="38">
         <v>784201754750582</v>
       </c>
-      <c r="F2" s="38">
+      <c r="F3" s="38">
         <v>784201668326545</v>
       </c>
-      <c r="G2" s="38">
+      <c r="G3" s="38">
         <v>784201724707522</v>
       </c>
-      <c r="H2" s="38">
+      <c r="H3" s="38">
         <v>784201724954983</v>
       </c>
-      <c r="I2" s="38">
+      <c r="I3" s="38">
         <v>784201786982161</v>
       </c>
-      <c r="J2" s="38">
+      <c r="J3" s="38">
         <v>784201715924243</v>
       </c>
-      <c r="K2" s="38">
+      <c r="K3" s="38">
         <v>784201796416309</v>
       </c>
-      <c r="L2" s="38">
+      <c r="L3" s="38">
         <v>784201786170999</v>
       </c>
-      <c r="M2" s="38">
+      <c r="M3" s="38">
         <v>784201686054061</v>
       </c>
-      <c r="N2" s="38">
+      <c r="N3" s="38">
         <v>784201686328036</v>
       </c>
-      <c r="O2" s="38">
+      <c r="O3" s="38">
         <v>784201685082469</v>
       </c>
-      <c r="P2" s="38">
+      <c r="P3" s="38">
         <v>784201709187971</v>
       </c>
-      <c r="Q2" s="38">
+      <c r="Q3" s="38">
         <v>784201705361653</v>
       </c>
-      <c r="R2" s="38">
+      <c r="R3" s="38">
         <v>784201706287253</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="18" customFormat="1" ht="57.6">
-      <c r="A3" s="26" t="s">
+    <row r="4" spans="1:18" s="18" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B4" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C4" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="R3" s="26" t="s">
+      <c r="R4" s="26" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="17" customFormat="1" ht="32.25">
-      <c r="A4" s="26" t="s">
+    <row r="5" spans="1:18" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B5" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C5" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D5" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E5" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F5" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G5" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H5" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I5" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="J5" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="K5" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="L5" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="M5" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="N5" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="O5" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="P5" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="Q5" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="R4" s="26" t="s">
+      <c r="R5" s="26" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="17" customFormat="1" ht="18">
-      <c r="A5" s="66" t="s">
+    <row r="6" spans="1:18" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A6" s="66" t="s">
         <v>275</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-    </row>
-    <row r="6" spans="1:18" s="16" customFormat="1" ht="18.75">
-      <c r="A6" s="47" t="s">
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+    </row>
+    <row r="7" spans="1:18" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B7" s="20">
         <v>77</v>
       </c>
-      <c r="C6" s="20">
-        <v>70</v>
-      </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20">
+      <c r="C7" s="20">
+        <v>70</v>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20">
         <v>96</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F7" s="20">
         <v>86</v>
       </c>
-      <c r="G6" s="20">
-        <v>70</v>
-      </c>
-      <c r="H6" s="20">
-        <v>90</v>
-      </c>
-      <c r="I6" s="20">
+      <c r="G7" s="20">
+        <v>70</v>
+      </c>
+      <c r="H7" s="20">
+        <v>90</v>
+      </c>
+      <c r="I7" s="20">
         <v>68</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J7" s="20">
         <v>55</v>
       </c>
-      <c r="K6" s="20">
-        <v>90</v>
-      </c>
-      <c r="L6" s="20">
+      <c r="K7" s="20">
+        <v>90</v>
+      </c>
+      <c r="L7" s="20">
         <v>92</v>
       </c>
-      <c r="M6" s="20">
+      <c r="M7" s="20">
         <v>94</v>
       </c>
-      <c r="N6" s="20">
+      <c r="N7" s="20">
         <v>66</v>
       </c>
-      <c r="O6" s="20">
-        <v>80</v>
-      </c>
-      <c r="P6" s="98">
+      <c r="O7" s="20">
+        <v>80</v>
+      </c>
+      <c r="P7" s="98">
         <v>50</v>
       </c>
-      <c r="Q6" s="98">
+      <c r="Q7" s="98">
         <v>55</v>
       </c>
-      <c r="R6" s="98">
+      <c r="R7" s="98">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="18.75">
-      <c r="A7" s="49" t="s">
+    <row r="8" spans="1:18" ht="18" x14ac:dyDescent="0.3">
+      <c r="A8" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B8" s="12">
         <v>60</v>
       </c>
-      <c r="C7" s="12">
-        <v>80</v>
-      </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12">
+      <c r="C8" s="12">
+        <v>80</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12">
         <v>100</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F8" s="12">
         <v>100</v>
       </c>
-      <c r="G7" s="12">
-        <v>70</v>
-      </c>
-      <c r="H7" s="12">
+      <c r="G8" s="12">
+        <v>70</v>
+      </c>
+      <c r="H8" s="12">
         <v>100</v>
       </c>
-      <c r="I7" s="12">
-        <v>70</v>
-      </c>
-      <c r="J7" s="12">
+      <c r="I8" s="12">
+        <v>70</v>
+      </c>
+      <c r="J8" s="12">
         <v>35</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K8" s="12">
         <v>85</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L8" s="12">
         <v>95</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M8" s="12">
         <v>100</v>
       </c>
-      <c r="N7" s="12">
-        <v>70</v>
-      </c>
-      <c r="O7" s="12">
+      <c r="N8" s="12">
+        <v>70</v>
+      </c>
+      <c r="O8" s="12">
         <v>100</v>
       </c>
-      <c r="P7" s="99">
-        <v>70</v>
-      </c>
-      <c r="Q7" s="99">
-        <v>80</v>
-      </c>
-      <c r="R7" s="99">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" s="16" customFormat="1" ht="18">
-      <c r="A8" s="47" t="s">
+      <c r="P8" s="99">
+        <v>70</v>
+      </c>
+      <c r="Q8" s="99">
+        <v>80</v>
+      </c>
+      <c r="R8" s="99">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A9" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="48"/>
-      <c r="R8" s="48"/>
-    </row>
-    <row r="9" spans="1:18" ht="18">
-      <c r="A9" s="49" t="s">
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="39"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+    </row>
+    <row r="10" spans="1:18" ht="18" x14ac:dyDescent="0.3">
+      <c r="A10" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="51"/>
-    </row>
-    <row r="10" spans="1:18" s="16" customFormat="1" ht="18">
-      <c r="A10" s="47" t="s">
+      <c r="B10" s="50"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="50"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="50"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="51"/>
+    </row>
+    <row r="11" spans="1:18" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A11" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="39">
+      <c r="B11" s="39">
         <v>60</v>
       </c>
-      <c r="C10" s="39">
+      <c r="C11" s="39">
         <v>50</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D11" s="39">
         <v>40</v>
       </c>
-      <c r="E10" s="39">
-        <v>80</v>
-      </c>
-      <c r="F10" s="39">
-        <v>70</v>
-      </c>
-      <c r="G10" s="39">
+      <c r="E11" s="39">
+        <v>80</v>
+      </c>
+      <c r="F11" s="39">
+        <v>70</v>
+      </c>
+      <c r="G11" s="39">
         <v>75</v>
       </c>
-      <c r="H10" s="39">
+      <c r="H11" s="39">
         <v>65</v>
       </c>
-      <c r="I10" s="39">
-        <v>70</v>
-      </c>
-      <c r="J10" s="39">
+      <c r="I11" s="39">
+        <v>70</v>
+      </c>
+      <c r="J11" s="39">
         <v>45</v>
       </c>
-      <c r="K10" s="39">
-        <v>70</v>
-      </c>
-      <c r="L10" s="39">
-        <v>80</v>
-      </c>
-      <c r="M10" s="39">
-        <v>80</v>
-      </c>
-      <c r="N10" s="39">
-        <v>70</v>
-      </c>
-      <c r="O10" s="39">
-        <v>70</v>
-      </c>
-      <c r="P10" s="48">
-        <v>70</v>
-      </c>
-      <c r="Q10" s="48">
+      <c r="K11" s="39">
+        <v>70</v>
+      </c>
+      <c r="L11" s="39">
+        <v>80</v>
+      </c>
+      <c r="M11" s="39">
+        <v>80</v>
+      </c>
+      <c r="N11" s="39">
+        <v>70</v>
+      </c>
+      <c r="O11" s="39">
+        <v>70</v>
+      </c>
+      <c r="P11" s="48">
+        <v>70</v>
+      </c>
+      <c r="Q11" s="48">
         <v>50</v>
       </c>
-      <c r="R10" s="48">
+      <c r="R11" s="48">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="18">
-      <c r="A11" s="49" t="s">
+    <row r="12" spans="1:18" ht="18" x14ac:dyDescent="0.3">
+      <c r="A12" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="50">
+      <c r="B12" s="50">
         <v>75</v>
       </c>
-      <c r="C11" s="50">
+      <c r="C12" s="50">
         <v>60</v>
       </c>
-      <c r="D11" s="50">
+      <c r="D12" s="50">
         <v>35</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E12" s="50">
         <v>85</v>
       </c>
-      <c r="F11" s="50">
-        <v>70</v>
-      </c>
-      <c r="G11" s="50">
+      <c r="F12" s="50">
+        <v>70</v>
+      </c>
+      <c r="G12" s="50">
         <v>75</v>
       </c>
-      <c r="H11" s="50">
+      <c r="H12" s="50">
         <v>89</v>
       </c>
-      <c r="I11" s="50">
-        <v>70</v>
-      </c>
-      <c r="J11" s="50">
+      <c r="I12" s="50">
+        <v>70</v>
+      </c>
+      <c r="J12" s="50">
         <v>65</v>
       </c>
-      <c r="K11" s="50">
-        <v>80</v>
-      </c>
-      <c r="L11" s="50">
-        <v>80</v>
-      </c>
-      <c r="M11" s="50">
+      <c r="K12" s="50">
+        <v>80</v>
+      </c>
+      <c r="L12" s="50">
+        <v>80</v>
+      </c>
+      <c r="M12" s="50">
         <v>85</v>
       </c>
-      <c r="N11" s="50">
+      <c r="N12" s="50">
         <v>75</v>
       </c>
-      <c r="O11" s="50">
+      <c r="O12" s="50">
         <v>75</v>
       </c>
-      <c r="P11" s="51">
+      <c r="P12" s="51">
         <v>69</v>
       </c>
-      <c r="Q11" s="51">
+      <c r="Q12" s="51">
         <v>40</v>
       </c>
-      <c r="R11" s="51">
+      <c r="R12" s="51">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-      <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12"/>
-      <c r="N12"/>
-      <c r="O12"/>
-      <c r="P12"/>
-      <c r="Q12"/>
-      <c r="R12"/>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13"/>
       <c r="P13"/>
       <c r="Q13"/>
       <c r="R13"/>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -10519,7 +10525,7 @@
       <c r="Q14"/>
       <c r="R14"/>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -10539,7 +10545,7 @@
       <c r="Q15"/>
       <c r="R15"/>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -10555,8 +10561,29 @@
       <c r="M16" s="13"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10564,38 +10591,38 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:Z15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46" style="17" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" style="17" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="17" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="17" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" style="17" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" style="17" customWidth="1"/>
-    <col min="8" max="8" width="21.85546875" style="17" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="17" customWidth="1"/>
+    <col min="2" max="2" width="39.5546875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" style="17" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="17" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="17" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" style="17" customWidth="1"/>
+    <col min="7" max="7" width="17.88671875" style="17" customWidth="1"/>
+    <col min="8" max="8" width="21.88671875" style="17" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" style="17" customWidth="1"/>
     <col min="10" max="10" width="24" style="17" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" style="17" customWidth="1"/>
-    <col min="12" max="12" width="17.7109375" style="17" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" style="17" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" style="17" customWidth="1"/>
     <col min="13" max="13" width="12" style="17" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" style="17" customWidth="1"/>
-    <col min="15" max="15" width="22.28515625" style="17" customWidth="1"/>
-    <col min="16" max="16" width="16.85546875" style="13" customWidth="1"/>
-    <col min="17" max="17" width="30.28515625" style="13" customWidth="1"/>
-    <col min="18" max="18" width="21.5703125" style="13" customWidth="1"/>
-    <col min="19" max="19" width="35.28515625" style="13" customWidth="1"/>
-    <col min="20" max="20" width="27.28515625" style="13" customWidth="1"/>
-    <col min="21" max="21" width="29.140625" style="13" customWidth="1"/>
-    <col min="22" max="22" width="30.140625" style="13" customWidth="1"/>
-    <col min="23" max="23" width="23.7109375" style="13" customWidth="1"/>
-    <col min="24" max="24" width="22.7109375" style="13" customWidth="1"/>
-    <col min="25" max="25" width="25.140625" style="13" customWidth="1"/>
-    <col min="26" max="26" width="23.5703125" style="13" customWidth="1"/>
-    <col min="27" max="16384" width="8.85546875" style="13"/>
+    <col min="14" max="14" width="13.33203125" style="17" customWidth="1"/>
+    <col min="15" max="15" width="22.33203125" style="17" customWidth="1"/>
+    <col min="16" max="16" width="16.88671875" style="13" customWidth="1"/>
+    <col min="17" max="17" width="30.33203125" style="13" customWidth="1"/>
+    <col min="18" max="18" width="21.5546875" style="13" customWidth="1"/>
+    <col min="19" max="19" width="35.33203125" style="13" customWidth="1"/>
+    <col min="20" max="20" width="27.33203125" style="13" customWidth="1"/>
+    <col min="21" max="21" width="29.109375" style="13" customWidth="1"/>
+    <col min="22" max="22" width="30.109375" style="13" customWidth="1"/>
+    <col min="23" max="23" width="23.6640625" style="13" customWidth="1"/>
+    <col min="24" max="24" width="22.6640625" style="13" customWidth="1"/>
+    <col min="25" max="25" width="25.109375" style="13" customWidth="1"/>
+    <col min="26" max="26" width="23.5546875" style="13" customWidth="1"/>
+    <col min="27" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="17" customFormat="1" ht="29.25">
+    <row r="1" spans="1:26" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -10675,7 +10702,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="17" customFormat="1" ht="15">
+    <row r="2" spans="1:26" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>281</v>
       </c>
@@ -10755,7 +10782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="17" customFormat="1" ht="15">
+    <row r="3" spans="1:26" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>16</v>
       </c>
@@ -10835,7 +10862,7 @@
         <v>784201631905292</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="18" customFormat="1" ht="101.25">
+    <row r="4" spans="1:26" s="18" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>17</v>
       </c>
@@ -10915,7 +10942,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="18" customFormat="1" ht="48">
+    <row r="5" spans="1:26" s="18" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
         <v>33</v>
       </c>
@@ -10995,7 +11022,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="20.25">
+    <row r="6" spans="1:26" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A6" s="44" t="s">
         <v>49</v>
       </c>
@@ -11025,7 +11052,7 @@
       <c r="Y6" s="45"/>
       <c r="Z6" s="45"/>
     </row>
-    <row r="7" spans="1:26" s="16" customFormat="1" ht="18.75">
+    <row r="7" spans="1:26" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="47" t="s">
         <v>50</v>
       </c>
@@ -11103,7 +11130,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="18.75">
+    <row r="8" spans="1:26" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="49" t="s">
         <v>51</v>
       </c>
@@ -11183,7 +11210,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="16" customFormat="1" ht="18.75">
+    <row r="9" spans="1:26" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="47" t="s">
         <v>52</v>
       </c>
@@ -11213,7 +11240,7 @@
       <c r="Y9" s="39"/>
       <c r="Z9" s="39"/>
     </row>
-    <row r="10" spans="1:26" ht="18.75">
+    <row r="10" spans="1:26" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="49" t="s">
         <v>53</v>
       </c>
@@ -11293,7 +11320,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="16" customFormat="1" ht="18.75">
+    <row r="11" spans="1:26" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="47" t="s">
         <v>54</v>
       </c>
@@ -11373,7 +11400,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="18.75">
+    <row r="12" spans="1:26" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="52" t="s">
         <v>55</v>
       </c>
@@ -11453,7 +11480,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="15">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
@@ -11468,7 +11495,7 @@
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -11494,7 +11521,7 @@
       <c r="Y14"/>
       <c r="Z14"/>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
@@ -11528,15 +11555,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:S15"/>
-  <sheetFormatPr defaultColWidth="19.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="19.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="15" width="19.42578125" style="17"/>
-    <col min="16" max="17" width="19.42578125" style="22"/>
-    <col min="18" max="19" width="19.42578125" style="17"/>
-    <col min="20" max="16384" width="19.42578125" style="13"/>
+    <col min="1" max="15" width="19.44140625" style="17"/>
+    <col min="16" max="17" width="19.44140625" style="22"/>
+    <col min="18" max="19" width="19.44140625" style="17"/>
+    <col min="20" max="16384" width="19.44140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="17" customFormat="1">
+    <row r="1" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -11595,7 +11622,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="17" customFormat="1">
+    <row r="2" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -11654,7 +11681,7 @@
         <v>784201574939159</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="17" customFormat="1" ht="43.5">
+    <row r="3" spans="1:19" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
@@ -11713,7 +11740,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="18" customFormat="1" ht="32.25">
+    <row r="4" spans="1:19" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>33</v>
       </c>
@@ -11772,7 +11799,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="20.25">
+    <row r="5" spans="1:19" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
         <v>49</v>
       </c>
@@ -11795,7 +11822,7 @@
       <c r="R5" s="45"/>
       <c r="S5" s="45"/>
     </row>
-    <row r="6" spans="1:19" s="16" customFormat="1" ht="18.75">
+    <row r="6" spans="1:19" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
@@ -11854,7 +11881,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="18.75">
+    <row r="7" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
@@ -11913,7 +11940,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="16" customFormat="1" ht="18.75">
+    <row r="8" spans="1:19" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
@@ -11936,7 +11963,7 @@
       <c r="R8" s="39"/>
       <c r="S8" s="39"/>
     </row>
-    <row r="9" spans="1:19" ht="18.75">
+    <row r="9" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="s">
         <v>53</v>
       </c>
@@ -11995,7 +12022,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="16" customFormat="1" ht="18.75">
+    <row r="10" spans="1:19" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>54</v>
       </c>
@@ -12054,7 +12081,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="18.75">
+    <row r="11" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="49" t="s">
         <v>55</v>
       </c>
@@ -12113,7 +12140,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
@@ -12132,7 +12159,7 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
@@ -12151,7 +12178,7 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -12170,7 +12197,7 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>

--- a/Midterm_Grades.xlsx
+++ b/Midterm_Grades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saraa\OneDrive - Emirates Schools Establishment\Attachments\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA74E1B5-32AD-41F6-95B3-DD075E8F6B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E7411F-8774-4292-BB75-EA6447220CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="541">
   <si>
     <t>Field</t>
   </si>
@@ -877,9 +877,6 @@
   </si>
   <si>
     <t>زاهره محمد مبارك الخييلي</t>
-  </si>
-  <si>
-    <t>Subjects</t>
   </si>
   <si>
     <t>Student 21</t>
@@ -1941,7 +1938,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2096,9 +2093,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2545,7 +2539,7 @@
       <c r="I3" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="86" t="s">
+      <c r="J3" s="85" t="s">
         <v>26</v>
       </c>
       <c r="K3" s="26" t="s">
@@ -3141,52 +3135,52 @@
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>367</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>368</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="D3" s="26" t="s">
         <v>369</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>370</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>372</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>373</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="I3" s="26" t="s">
         <v>374</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="J3" s="26" t="s">
         <v>375</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="K3" s="26" t="s">
         <v>376</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="L3" s="26" t="s">
         <v>377</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="M3" s="26" t="s">
         <v>378</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="N3" s="26" t="s">
         <v>379</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="O3" s="26" t="s">
         <v>380</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="P3" s="26" t="s">
         <v>381</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="Q3" s="26" t="s">
         <v>382</v>
-      </c>
-      <c r="Q3" s="26" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -3194,72 +3188,72 @@
         <v>33</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>383</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>384</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>385</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>386</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>387</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>388</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>389</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>390</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>391</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>392</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>393</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>395</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>396</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>397</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>398</v>
       </c>
-      <c r="Q4" s="26" t="s">
-        <v>399</v>
-      </c>
     </row>
     <row r="5" spans="1:17" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="70"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
       <c r="P5" s="33"/>
       <c r="Q5" s="33"/>
     </row>
@@ -3267,46 +3261,46 @@
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="100">
-        <v>70</v>
-      </c>
-      <c r="C6" s="100">
+      <c r="B6" s="99">
+        <v>70</v>
+      </c>
+      <c r="C6" s="99">
         <v>68</v>
       </c>
-      <c r="D6" s="100">
-        <v>70</v>
-      </c>
-      <c r="E6" s="100">
+      <c r="D6" s="99">
+        <v>70</v>
+      </c>
+      <c r="E6" s="99">
         <v>68</v>
       </c>
-      <c r="F6" s="100">
-        <v>90</v>
-      </c>
-      <c r="G6" s="100">
+      <c r="F6" s="99">
+        <v>90</v>
+      </c>
+      <c r="G6" s="99">
         <v>45</v>
       </c>
-      <c r="H6" s="100">
+      <c r="H6" s="99">
         <v>67</v>
       </c>
-      <c r="I6" s="100">
+      <c r="I6" s="99">
         <v>66</v>
       </c>
-      <c r="J6" s="100">
+      <c r="J6" s="99">
         <v>45</v>
       </c>
-      <c r="K6" s="100">
+      <c r="K6" s="99">
         <v>45</v>
       </c>
-      <c r="L6" s="100">
-        <v>70</v>
-      </c>
-      <c r="M6" s="100">
+      <c r="L6" s="99">
+        <v>70</v>
+      </c>
+      <c r="M6" s="99">
         <v>45</v>
       </c>
-      <c r="N6" s="100">
+      <c r="N6" s="99">
         <v>66</v>
       </c>
-      <c r="O6" s="100">
+      <c r="O6" s="99">
         <v>77</v>
       </c>
       <c r="P6" s="5">
@@ -3320,46 +3314,46 @@
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="95">
-        <v>70</v>
-      </c>
-      <c r="C7" s="95">
-        <v>70</v>
-      </c>
-      <c r="D7" s="95">
-        <v>80</v>
-      </c>
-      <c r="E7" s="95">
+      <c r="B7" s="94">
+        <v>70</v>
+      </c>
+      <c r="C7" s="94">
+        <v>70</v>
+      </c>
+      <c r="D7" s="94">
+        <v>80</v>
+      </c>
+      <c r="E7" s="94">
         <v>50</v>
       </c>
-      <c r="F7" s="95">
-        <v>90</v>
-      </c>
-      <c r="G7" s="95">
+      <c r="F7" s="94">
+        <v>90</v>
+      </c>
+      <c r="G7" s="94">
         <v>40</v>
       </c>
-      <c r="H7" s="95">
-        <v>90</v>
-      </c>
-      <c r="I7" s="95">
-        <v>70</v>
-      </c>
-      <c r="J7" s="95">
+      <c r="H7" s="94">
+        <v>90</v>
+      </c>
+      <c r="I7" s="94">
+        <v>70</v>
+      </c>
+      <c r="J7" s="94">
         <v>60</v>
       </c>
-      <c r="K7" s="95">
+      <c r="K7" s="94">
         <v>50</v>
       </c>
-      <c r="L7" s="95">
-        <v>70</v>
-      </c>
-      <c r="M7" s="95">
+      <c r="L7" s="94">
+        <v>70</v>
+      </c>
+      <c r="M7" s="94">
         <v>60</v>
       </c>
-      <c r="N7" s="95">
+      <c r="N7" s="94">
         <v>60</v>
       </c>
-      <c r="O7" s="95">
+      <c r="O7" s="94">
         <v>80</v>
       </c>
       <c r="P7" s="4">
@@ -3373,20 +3367,20 @@
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
-      <c r="M8" s="71"/>
-      <c r="N8" s="71"/>
-      <c r="O8" s="71"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="70"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="70"/>
       <c r="P8" s="31"/>
       <c r="Q8" s="31"/>
     </row>
@@ -3394,46 +3388,46 @@
       <c r="A9" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="95">
+      <c r="B9" s="94">
         <v>77</v>
       </c>
-      <c r="C9" s="95">
+      <c r="C9" s="94">
         <v>54</v>
       </c>
-      <c r="D9" s="95">
+      <c r="D9" s="94">
         <v>74</v>
       </c>
-      <c r="E9" s="95">
+      <c r="E9" s="94">
         <v>60</v>
       </c>
-      <c r="F9" s="95">
+      <c r="F9" s="94">
         <v>94</v>
       </c>
-      <c r="G9" s="95">
+      <c r="G9" s="94">
         <v>37</v>
       </c>
-      <c r="H9" s="95">
+      <c r="H9" s="94">
         <v>95</v>
       </c>
-      <c r="I9" s="95">
+      <c r="I9" s="94">
         <v>37</v>
       </c>
-      <c r="J9" s="95">
+      <c r="J9" s="94">
         <v>32</v>
       </c>
-      <c r="K9" s="95">
+      <c r="K9" s="94">
         <v>22</v>
       </c>
-      <c r="L9" s="95">
+      <c r="L9" s="94">
         <v>57</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="94">
         <v>85</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="94">
         <v>50</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="94">
         <v>60</v>
       </c>
       <c r="P9" s="4">
@@ -3447,46 +3441,46 @@
       <c r="A10" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="71">
+      <c r="B10" s="70">
         <v>85</v>
       </c>
-      <c r="C10" s="71">
+      <c r="C10" s="70">
         <v>67</v>
       </c>
-      <c r="D10" s="71">
+      <c r="D10" s="70">
         <v>86</v>
       </c>
-      <c r="E10" s="71">
-        <v>80</v>
-      </c>
-      <c r="F10" s="71">
+      <c r="E10" s="70">
+        <v>80</v>
+      </c>
+      <c r="F10" s="70">
         <v>95</v>
       </c>
-      <c r="G10" s="71">
+      <c r="G10" s="70">
         <v>46</v>
       </c>
-      <c r="H10" s="71">
+      <c r="H10" s="70">
         <v>93</v>
       </c>
-      <c r="I10" s="71">
+      <c r="I10" s="70">
         <v>65</v>
       </c>
-      <c r="J10" s="71">
+      <c r="J10" s="70">
         <v>37</v>
       </c>
-      <c r="K10" s="71">
+      <c r="K10" s="70">
         <v>61</v>
       </c>
-      <c r="L10" s="71">
+      <c r="L10" s="70">
         <v>79</v>
       </c>
-      <c r="M10" s="71">
+      <c r="M10" s="70">
         <v>93</v>
       </c>
-      <c r="N10" s="71">
+      <c r="N10" s="70">
         <v>67</v>
       </c>
-      <c r="O10" s="71">
+      <c r="O10" s="70">
         <v>75</v>
       </c>
       <c r="P10" s="31">
@@ -3777,64 +3771,64 @@
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>399</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>400</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="D3" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>402</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>403</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>404</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>405</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="I3" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="J3" s="26" t="s">
         <v>407</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="K3" s="26" t="s">
         <v>408</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="L3" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="M3" s="26" t="s">
         <v>410</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="N3" s="26" t="s">
         <v>411</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="O3" s="26" t="s">
         <v>412</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="P3" s="26" t="s">
         <v>413</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="Q3" s="26" t="s">
         <v>414</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="R3" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="R3" s="26" t="s">
+      <c r="S3" s="26" t="s">
         <v>416</v>
       </c>
-      <c r="S3" s="26" t="s">
+      <c r="T3" s="26" t="s">
         <v>417</v>
       </c>
-      <c r="T3" s="26" t="s">
+      <c r="U3" s="26" t="s">
         <v>418</v>
-      </c>
-      <c r="U3" s="26" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="4" spans="1:21" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -3842,84 +3836,84 @@
         <v>33</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>419</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>420</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>422</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>423</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>424</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>425</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>426</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>427</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>428</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>429</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>430</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>431</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>432</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>433</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>434</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="R4" s="26" t="s">
         <v>435</v>
       </c>
-      <c r="R4" s="26" t="s">
+      <c r="S4" s="26" t="s">
         <v>436</v>
       </c>
-      <c r="S4" s="26" t="s">
+      <c r="T4" s="26" t="s">
         <v>437</v>
       </c>
-      <c r="T4" s="26" t="s">
+      <c r="U4" s="26" t="s">
         <v>438</v>
       </c>
-      <c r="U4" s="26" t="s">
-        <v>439</v>
-      </c>
     </row>
     <row r="5" spans="1:21" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="70"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
       <c r="P5" s="33"/>
       <c r="Q5" s="33"/>
       <c r="R5" s="33"/>
@@ -3931,46 +3925,46 @@
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="100">
-        <v>90</v>
-      </c>
-      <c r="C6" s="100">
+      <c r="B6" s="99">
+        <v>90</v>
+      </c>
+      <c r="C6" s="99">
         <v>68</v>
       </c>
-      <c r="D6" s="100">
-        <v>80</v>
-      </c>
-      <c r="E6" s="100">
-        <v>80</v>
-      </c>
-      <c r="F6" s="100">
+      <c r="D6" s="99">
+        <v>80</v>
+      </c>
+      <c r="E6" s="99">
+        <v>80</v>
+      </c>
+      <c r="F6" s="99">
         <v>88</v>
       </c>
-      <c r="G6" s="100">
+      <c r="G6" s="99">
         <v>84</v>
       </c>
-      <c r="H6" s="100">
+      <c r="H6" s="99">
         <v>66</v>
       </c>
-      <c r="I6" s="100">
-        <v>70</v>
-      </c>
-      <c r="J6" s="100">
+      <c r="I6" s="99">
+        <v>70</v>
+      </c>
+      <c r="J6" s="99">
         <v>77</v>
       </c>
-      <c r="K6" s="100">
+      <c r="K6" s="99">
         <v>66</v>
       </c>
-      <c r="L6" s="100">
-        <v>90</v>
-      </c>
-      <c r="M6" s="100">
+      <c r="L6" s="99">
+        <v>90</v>
+      </c>
+      <c r="M6" s="99">
         <v>74</v>
       </c>
-      <c r="N6" s="100">
+      <c r="N6" s="99">
         <v>88</v>
       </c>
-      <c r="O6" s="100">
+      <c r="O6" s="99">
         <v>77</v>
       </c>
       <c r="P6" s="5">
@@ -3996,46 +3990,46 @@
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="95">
-        <v>90</v>
-      </c>
-      <c r="C7" s="95">
+      <c r="B7" s="94">
+        <v>90</v>
+      </c>
+      <c r="C7" s="94">
         <v>60</v>
       </c>
-      <c r="D7" s="95">
-        <v>90</v>
-      </c>
-      <c r="E7" s="95">
-        <v>90</v>
-      </c>
-      <c r="F7" s="95">
-        <v>70</v>
-      </c>
-      <c r="G7" s="95">
-        <v>80</v>
-      </c>
-      <c r="H7" s="95">
-        <v>70</v>
-      </c>
-      <c r="I7" s="95">
+      <c r="D7" s="94">
+        <v>90</v>
+      </c>
+      <c r="E7" s="94">
+        <v>90</v>
+      </c>
+      <c r="F7" s="94">
+        <v>70</v>
+      </c>
+      <c r="G7" s="94">
+        <v>80</v>
+      </c>
+      <c r="H7" s="94">
+        <v>70</v>
+      </c>
+      <c r="I7" s="94">
         <v>60</v>
       </c>
-      <c r="J7" s="95">
-        <v>80</v>
-      </c>
-      <c r="K7" s="95">
-        <v>90</v>
-      </c>
-      <c r="L7" s="95">
-        <v>90</v>
-      </c>
-      <c r="M7" s="95">
-        <v>80</v>
-      </c>
-      <c r="N7" s="95">
-        <v>90</v>
-      </c>
-      <c r="O7" s="95">
+      <c r="J7" s="94">
+        <v>80</v>
+      </c>
+      <c r="K7" s="94">
+        <v>90</v>
+      </c>
+      <c r="L7" s="94">
+        <v>90</v>
+      </c>
+      <c r="M7" s="94">
+        <v>80</v>
+      </c>
+      <c r="N7" s="94">
+        <v>90</v>
+      </c>
+      <c r="O7" s="94">
         <v>70</v>
       </c>
       <c r="P7" s="4">
@@ -4061,46 +4055,46 @@
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="71">
-        <v>90</v>
-      </c>
-      <c r="C8" s="71">
+      <c r="B8" s="70">
+        <v>90</v>
+      </c>
+      <c r="C8" s="70">
         <v>60</v>
       </c>
-      <c r="D8" s="71">
-        <v>80</v>
-      </c>
-      <c r="E8" s="71">
+      <c r="D8" s="70">
+        <v>80</v>
+      </c>
+      <c r="E8" s="70">
         <v>86</v>
       </c>
-      <c r="F8" s="71">
-        <v>90</v>
-      </c>
-      <c r="G8" s="71">
+      <c r="F8" s="70">
+        <v>90</v>
+      </c>
+      <c r="G8" s="70">
         <v>88</v>
       </c>
-      <c r="H8" s="71">
+      <c r="H8" s="70">
         <v>64</v>
       </c>
-      <c r="I8" s="71">
+      <c r="I8" s="70">
         <v>82</v>
       </c>
-      <c r="J8" s="71">
+      <c r="J8" s="70">
         <v>84</v>
       </c>
-      <c r="K8" s="71">
+      <c r="K8" s="70">
         <v>71</v>
       </c>
-      <c r="L8" s="71">
-        <v>90</v>
-      </c>
-      <c r="M8" s="71">
+      <c r="L8" s="70">
+        <v>90</v>
+      </c>
+      <c r="M8" s="70">
         <v>60</v>
       </c>
-      <c r="N8" s="71">
-        <v>90</v>
-      </c>
-      <c r="O8" s="71">
+      <c r="N8" s="70">
+        <v>90</v>
+      </c>
+      <c r="O8" s="70">
         <v>80</v>
       </c>
       <c r="P8" s="31">
@@ -4151,46 +4145,46 @@
       <c r="A10" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="71">
-        <v>80</v>
-      </c>
-      <c r="C10" s="71">
+      <c r="B10" s="70">
+        <v>80</v>
+      </c>
+      <c r="C10" s="70">
         <v>62</v>
       </c>
-      <c r="D10" s="71">
+      <c r="D10" s="70">
         <v>49</v>
       </c>
-      <c r="E10" s="71">
+      <c r="E10" s="70">
         <v>82</v>
       </c>
-      <c r="F10" s="71">
+      <c r="F10" s="70">
         <v>76</v>
       </c>
-      <c r="G10" s="71">
+      <c r="G10" s="70">
         <v>59</v>
       </c>
-      <c r="H10" s="71">
+      <c r="H10" s="70">
         <v>62</v>
       </c>
-      <c r="I10" s="71">
+      <c r="I10" s="70">
         <v>54</v>
       </c>
-      <c r="J10" s="71">
+      <c r="J10" s="70">
         <v>74</v>
       </c>
-      <c r="K10" s="71">
+      <c r="K10" s="70">
         <v>43</v>
       </c>
-      <c r="L10" s="71">
+      <c r="L10" s="70">
         <v>72</v>
       </c>
-      <c r="M10" s="71">
+      <c r="M10" s="70">
         <v>60</v>
       </c>
-      <c r="N10" s="71">
+      <c r="N10" s="70">
         <v>82</v>
       </c>
-      <c r="O10" s="71">
+      <c r="O10" s="70">
         <v>58</v>
       </c>
       <c r="P10" s="31">
@@ -4428,7 +4422,7 @@
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="72">
+      <c r="B2" s="71">
         <v>784201238541979</v>
       </c>
       <c r="C2" s="38">
@@ -4484,112 +4478,112 @@
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="72" t="s">
+        <v>439</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>440</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="D3" s="26" t="s">
         <v>441</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>442</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>443</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>444</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>445</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="I3" s="26" t="s">
         <v>446</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="J3" s="26" t="s">
         <v>447</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="K3" s="26" t="s">
         <v>448</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="L3" s="26" t="s">
         <v>449</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="M3" s="26" t="s">
         <v>450</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="N3" s="26" t="s">
         <v>451</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="O3" s="26" t="s">
         <v>452</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="P3" s="26" t="s">
         <v>453</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="Q3" s="26" t="s">
         <v>454</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="R3" s="26" t="s">
         <v>455</v>
-      </c>
-      <c r="R3" s="26" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="4" spans="1:18" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="73" t="s">
+        <v>456</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>457</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>458</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>459</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>460</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>461</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>462</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>463</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>464</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>465</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>466</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>467</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>468</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>469</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>470</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>471</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="R4" s="26" t="s">
         <v>472</v>
-      </c>
-      <c r="R4" s="26" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="19.2" x14ac:dyDescent="0.3">
@@ -5071,13 +5065,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>475</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -5085,13 +5079,13 @@
         <v>33</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>478</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.2" x14ac:dyDescent="0.3">
@@ -5160,15 +5154,15 @@
     </row>
     <row r="10" spans="1:4" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B10" s="5">
         <v>85</v>
       </c>
-      <c r="C10" s="75">
+      <c r="C10" s="74">
         <v>92</v>
       </c>
-      <c r="D10" s="75">
+      <c r="D10" s="74">
         <v>85</v>
       </c>
     </row>
@@ -5188,7 +5182,7 @@
     </row>
     <row r="12" spans="1:4" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="29">
         <v>94</v>
@@ -5319,43 +5313,43 @@
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>481</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>482</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="D3" s="26" t="s">
         <v>483</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>484</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>485</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>486</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>487</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="I3" s="26" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="J3" s="26" t="s">
         <v>489</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="K3" s="26" t="s">
         <v>490</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="L3" s="26" t="s">
         <v>491</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="M3" s="26" t="s">
         <v>492</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="N3" s="26" t="s">
         <v>493</v>
-      </c>
-      <c r="N3" s="26" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -5363,43 +5357,43 @@
         <v>33</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>494</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>495</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>498</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>499</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>500</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>501</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>502</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>503</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>504</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>505</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>506</v>
-      </c>
-      <c r="N4" s="26" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="19.2" x14ac:dyDescent="0.3">
@@ -5788,40 +5782,40 @@
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>507</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>508</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="D3" s="26" t="s">
         <v>509</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>510</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>511</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>512</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>513</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="I3" s="26" t="s">
         <v>514</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="J3" s="26" t="s">
         <v>515</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="K3" s="26" t="s">
         <v>516</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="L3" s="26" t="s">
         <v>517</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="M3" s="26" t="s">
         <v>518</v>
-      </c>
-      <c r="M3" s="26" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -5829,102 +5823,102 @@
         <v>33</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>519</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>520</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>521</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>522</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>523</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>524</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>525</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>526</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>527</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>528</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>529</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>530</v>
       </c>
-      <c r="M4" s="26" t="s">
-        <v>531</v>
-      </c>
     </row>
     <row r="5" spans="1:13" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
     </row>
     <row r="6" spans="1:13" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="79">
+      <c r="B6" s="78">
         <v>65</v>
       </c>
-      <c r="C6" s="79">
+      <c r="C6" s="78">
         <v>50</v>
       </c>
-      <c r="D6" s="79">
+      <c r="D6" s="78">
         <v>65</v>
       </c>
-      <c r="E6" s="79">
+      <c r="E6" s="78">
         <v>75</v>
       </c>
-      <c r="F6" s="79">
+      <c r="F6" s="78">
         <v>75</v>
       </c>
-      <c r="G6" s="79">
-        <v>80</v>
-      </c>
-      <c r="H6" s="79">
+      <c r="G6" s="78">
+        <v>80</v>
+      </c>
+      <c r="H6" s="78">
         <v>75</v>
       </c>
-      <c r="I6" s="79">
-        <v>80</v>
-      </c>
-      <c r="J6" s="79">
-        <v>80</v>
-      </c>
-      <c r="K6" s="79">
+      <c r="I6" s="78">
+        <v>80</v>
+      </c>
+      <c r="J6" s="78">
+        <v>80</v>
+      </c>
+      <c r="K6" s="78">
         <v>75</v>
       </c>
-      <c r="L6" s="79">
-        <v>80</v>
-      </c>
-      <c r="M6" s="79">
+      <c r="L6" s="78">
+        <v>80</v>
+      </c>
+      <c r="M6" s="78">
         <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="77" t="s">
         <v>51</v>
       </c>
       <c r="B7" s="26">
@@ -5965,69 +5959,69 @@
       </c>
     </row>
     <row r="8" spans="1:13" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A8" s="77" t="s">
+      <c r="A8" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="79">
-        <v>70</v>
-      </c>
-      <c r="C8" s="79">
+      <c r="B8" s="78">
+        <v>70</v>
+      </c>
+      <c r="C8" s="78">
         <v>60</v>
       </c>
-      <c r="D8" s="79">
+      <c r="D8" s="78">
         <v>50</v>
       </c>
-      <c r="E8" s="79">
+      <c r="E8" s="78">
         <v>78</v>
       </c>
-      <c r="F8" s="79">
+      <c r="F8" s="78">
         <v>82</v>
       </c>
-      <c r="G8" s="79">
+      <c r="G8" s="78">
         <v>86</v>
       </c>
-      <c r="H8" s="79">
+      <c r="H8" s="78">
         <v>84</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="78">
         <v>76</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="78">
         <v>78</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="78">
         <v>72</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="78">
         <v>76</v>
       </c>
-      <c r="M8" s="79">
+      <c r="M8" s="78">
         <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="92">
+      <c r="B9" s="91">
         <v>69</v>
       </c>
-      <c r="C9" s="92">
+      <c r="C9" s="91">
         <v>81</v>
       </c>
-      <c r="D9" s="92">
+      <c r="D9" s="91">
         <v>95</v>
       </c>
-      <c r="E9" s="92">
-        <v>70</v>
-      </c>
-      <c r="F9" s="92">
-        <v>70</v>
-      </c>
-      <c r="G9" s="92">
+      <c r="E9" s="91">
+        <v>70</v>
+      </c>
+      <c r="F9" s="91">
+        <v>70</v>
+      </c>
+      <c r="G9" s="91">
         <v>85</v>
       </c>
-      <c r="H9" s="93">
+      <c r="H9" s="92">
         <v>82</v>
       </c>
       <c r="I9" s="57">
@@ -6039,7 +6033,7 @@
       <c r="K9" s="57">
         <v>75</v>
       </c>
-      <c r="L9" s="94">
+      <c r="L9" s="93">
         <v>82.5</v>
       </c>
       <c r="M9" s="57">
@@ -6047,44 +6041,44 @@
       </c>
     </row>
     <row r="10" spans="1:13" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A10" s="77" t="s">
-        <v>532</v>
-      </c>
-      <c r="B10" s="79">
+      <c r="A10" s="76" t="s">
+        <v>531</v>
+      </c>
+      <c r="B10" s="78">
         <v>64</v>
       </c>
-      <c r="C10" s="79">
+      <c r="C10" s="78">
         <v>40</v>
       </c>
-      <c r="D10" s="79">
+      <c r="D10" s="78">
         <v>36</v>
       </c>
-      <c r="E10" s="79">
+      <c r="E10" s="78">
         <v>60</v>
       </c>
-      <c r="F10" s="79">
+      <c r="F10" s="78">
         <v>76</v>
       </c>
-      <c r="G10" s="79">
+      <c r="G10" s="78">
         <v>88</v>
       </c>
-      <c r="H10" s="79">
+      <c r="H10" s="78">
         <v>60</v>
       </c>
-      <c r="I10" s="79">
+      <c r="I10" s="78">
         <v>76</v>
       </c>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79">
+      <c r="J10" s="78"/>
+      <c r="K10" s="78">
         <v>72</v>
       </c>
-      <c r="L10" s="79"/>
-      <c r="M10" s="79">
+      <c r="L10" s="78"/>
+      <c r="M10" s="78">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="18" x14ac:dyDescent="0.3">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="77" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="26">
@@ -6125,43 +6119,43 @@
       </c>
     </row>
     <row r="12" spans="1:13" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A12" s="77" t="s">
-        <v>481</v>
-      </c>
-      <c r="B12" s="79">
-        <v>80</v>
-      </c>
-      <c r="C12" s="79">
+      <c r="A12" s="76" t="s">
+        <v>480</v>
+      </c>
+      <c r="B12" s="78">
+        <v>80</v>
+      </c>
+      <c r="C12" s="78">
         <v>60</v>
       </c>
-      <c r="D12" s="79">
-        <v>80</v>
-      </c>
-      <c r="E12" s="79">
-        <v>90</v>
-      </c>
-      <c r="F12" s="79">
+      <c r="D12" s="78">
+        <v>80</v>
+      </c>
+      <c r="E12" s="78">
+        <v>90</v>
+      </c>
+      <c r="F12" s="78">
         <v>88</v>
       </c>
-      <c r="G12" s="79">
+      <c r="G12" s="78">
         <v>91</v>
       </c>
-      <c r="H12" s="79">
+      <c r="H12" s="78">
         <v>64</v>
       </c>
-      <c r="I12" s="79">
+      <c r="I12" s="78">
         <v>85</v>
       </c>
-      <c r="J12" s="79">
+      <c r="J12" s="78">
         <v>83</v>
       </c>
-      <c r="K12" s="79">
+      <c r="K12" s="78">
         <v>83</v>
       </c>
-      <c r="L12" s="79">
+      <c r="L12" s="78">
         <v>74</v>
       </c>
-      <c r="M12" s="79">
+      <c r="M12" s="78">
         <v>78</v>
       </c>
     </row>
@@ -6210,7 +6204,7 @@
       <c r="B2" s="38">
         <v>784201040962751</v>
       </c>
-      <c r="C2" s="85">
+      <c r="C2" s="84">
         <v>784201035410485</v>
       </c>
       <c r="D2" s="64">
@@ -6228,19 +6222,19 @@
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>532</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>533</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="D3" s="26" t="s">
         <v>534</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>535</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>536</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -6248,38 +6242,38 @@
         <v>33</v>
       </c>
       <c r="B4" s="27"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
     </row>
     <row r="5" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
     </row>
     <row r="6" spans="1:6" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="97">
-        <v>90</v>
-      </c>
-      <c r="C6" s="96">
+      <c r="B6" s="96">
+        <v>90</v>
+      </c>
+      <c r="C6" s="95">
         <v>95</v>
       </c>
-      <c r="D6" s="96">
+      <c r="D6" s="95">
         <v>87</v>
       </c>
-      <c r="E6" s="96">
+      <c r="E6" s="95">
         <v>97</v>
       </c>
-      <c r="F6" s="96">
+      <c r="F6" s="95">
         <v>96</v>
       </c>
     </row>
@@ -6287,19 +6281,19 @@
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="88">
-        <v>90</v>
-      </c>
-      <c r="C7" s="84">
-        <v>90</v>
-      </c>
-      <c r="D7" s="84">
-        <v>90</v>
-      </c>
-      <c r="E7" s="84">
+      <c r="B7" s="87">
+        <v>90</v>
+      </c>
+      <c r="C7" s="83">
+        <v>90</v>
+      </c>
+      <c r="D7" s="83">
+        <v>90</v>
+      </c>
+      <c r="E7" s="83">
         <v>100</v>
       </c>
-      <c r="F7" s="84">
+      <c r="F7" s="83">
         <v>90</v>
       </c>
     </row>
@@ -6307,19 +6301,19 @@
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="89">
-        <v>80</v>
-      </c>
-      <c r="C8" s="83">
-        <v>90</v>
-      </c>
-      <c r="D8" s="83">
+      <c r="B8" s="88">
+        <v>80</v>
+      </c>
+      <c r="C8" s="82">
+        <v>90</v>
+      </c>
+      <c r="D8" s="82">
         <v>91</v>
       </c>
-      <c r="E8" s="83">
+      <c r="E8" s="82">
         <v>96</v>
       </c>
-      <c r="F8" s="83">
+      <c r="F8" s="82">
         <v>92</v>
       </c>
     </row>
@@ -6327,39 +6321,39 @@
       <c r="A9" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="91">
+      <c r="B9" s="90">
         <v>100</v>
       </c>
-      <c r="C9" s="90">
+      <c r="C9" s="89">
         <v>99</v>
       </c>
-      <c r="D9" s="90">
+      <c r="D9" s="89">
         <v>100</v>
       </c>
-      <c r="E9" s="90">
+      <c r="E9" s="89">
         <v>99</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="89">
         <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
-        <v>480</v>
-      </c>
-      <c r="B10" s="89">
-        <v>90</v>
-      </c>
-      <c r="C10" s="83">
+        <v>479</v>
+      </c>
+      <c r="B10" s="88">
+        <v>90</v>
+      </c>
+      <c r="C10" s="82">
         <v>85</v>
       </c>
-      <c r="D10" s="83">
+      <c r="D10" s="82">
         <v>85</v>
       </c>
-      <c r="E10" s="83">
-        <v>90</v>
-      </c>
-      <c r="F10" s="83">
+      <c r="E10" s="82">
+        <v>90</v>
+      </c>
+      <c r="F10" s="82">
         <v>90</v>
       </c>
     </row>
@@ -6367,59 +6361,59 @@
       <c r="A11" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="88">
+      <c r="B11" s="87">
         <v>96</v>
       </c>
-      <c r="C11" s="84">
+      <c r="C11" s="83">
         <v>84</v>
       </c>
-      <c r="D11" s="84">
+      <c r="D11" s="83">
         <v>91</v>
       </c>
-      <c r="E11" s="84">
+      <c r="E11" s="83">
         <v>99</v>
       </c>
-      <c r="F11" s="84">
+      <c r="F11" s="83">
         <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
-        <v>481</v>
-      </c>
-      <c r="B12" s="89">
+        <v>480</v>
+      </c>
+      <c r="B12" s="88">
         <v>100</v>
       </c>
-      <c r="C12" s="83">
+      <c r="C12" s="82">
         <v>94</v>
       </c>
-      <c r="D12" s="83">
+      <c r="D12" s="82">
         <v>100</v>
       </c>
-      <c r="E12" s="83">
+      <c r="E12" s="82">
         <v>100</v>
       </c>
-      <c r="F12" s="83">
+      <c r="F12" s="82">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="49" t="s">
-        <v>532</v>
-      </c>
-      <c r="B13" s="88">
+        <v>531</v>
+      </c>
+      <c r="B13" s="87">
         <v>100</v>
       </c>
-      <c r="C13" s="84">
+      <c r="C13" s="83">
         <v>88</v>
       </c>
-      <c r="D13" s="84">
+      <c r="D13" s="83">
         <v>100</v>
       </c>
-      <c r="E13" s="84">
+      <c r="E13" s="83">
         <v>100</v>
       </c>
-      <c r="F13" s="84">
+      <c r="F13" s="83">
         <v>100</v>
       </c>
     </row>
@@ -6468,10 +6462,10 @@
         <v>17</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>538</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -6479,10 +6473,10 @@
         <v>33</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>540</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="19.2" x14ac:dyDescent="0.3">
@@ -6538,7 +6532,7 @@
     </row>
     <row r="10" spans="1:3" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B10" s="5">
         <v>56</v>
@@ -6558,7 +6552,7 @@
     </row>
     <row r="12" spans="1:3" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="5">
         <v>85</v>
@@ -6693,52 +6687,52 @@
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="86" t="s">
+      <c r="C3" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="86" t="s">
+      <c r="E3" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="87" t="s">
+      <c r="F3" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="86" t="s">
+      <c r="G3" s="85" t="s">
         <v>62</v>
       </c>
-      <c r="H3" s="86" t="s">
+      <c r="H3" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="86" t="s">
+      <c r="I3" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="86" t="s">
+      <c r="J3" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="K3" s="86" t="s">
+      <c r="K3" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="L3" s="86" t="s">
+      <c r="L3" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="M3" s="86" t="s">
+      <c r="M3" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="N3" s="86" t="s">
+      <c r="N3" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="O3" s="86" t="s">
-        <v>70</v>
-      </c>
-      <c r="P3" s="86" t="s">
+      <c r="O3" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="P3" s="85" t="s">
         <v>71</v>
       </c>
-      <c r="Q3" s="86" t="s">
+      <c r="Q3" s="85" t="s">
         <v>72</v>
       </c>
     </row>
@@ -10201,27 +10195,27 @@
         <v>274</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A6" s="66" t="s">
-        <v>275</v>
-      </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="67"/>
-      <c r="R6" s="67"/>
+    <row r="6" spans="1:18" s="17" customFormat="1" ht="19.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="66"/>
+      <c r="P6" s="66"/>
+      <c r="Q6" s="66"/>
+      <c r="R6" s="66"/>
     </row>
     <row r="7" spans="1:18" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="47" t="s">
@@ -10267,13 +10261,13 @@
       <c r="O7" s="20">
         <v>80</v>
       </c>
-      <c r="P7" s="98">
+      <c r="P7" s="97">
         <v>50</v>
       </c>
-      <c r="Q7" s="98">
+      <c r="Q7" s="97">
         <v>55</v>
       </c>
-      <c r="R7" s="98">
+      <c r="R7" s="97">
         <v>55</v>
       </c>
     </row>
@@ -10321,13 +10315,13 @@
       <c r="O8" s="12">
         <v>100</v>
       </c>
-      <c r="P8" s="99">
-        <v>70</v>
-      </c>
-      <c r="Q8" s="99">
-        <v>80</v>
-      </c>
-      <c r="R8" s="99">
+      <c r="P8" s="98">
+        <v>70</v>
+      </c>
+      <c r="Q8" s="98">
+        <v>80</v>
+      </c>
+      <c r="R8" s="98">
         <v>80</v>
       </c>
     </row>
@@ -10565,23 +10559,7 @@
       <c r="Q16"/>
       <c r="R16"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-    </row>
+    <row r="17" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10687,24 +10665,24 @@
         <v>162</v>
       </c>
       <c r="V1" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="W1" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="W1" s="26" t="s">
+      <c r="X1" s="26" t="s">
         <v>277</v>
       </c>
-      <c r="X1" s="26" t="s">
+      <c r="Y1" s="26" t="s">
         <v>278</v>
       </c>
-      <c r="Y1" s="26" t="s">
+      <c r="Z1" s="26" t="s">
         <v>279</v>
-      </c>
-      <c r="Z1" s="26" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:26" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B2" s="26">
         <v>1</v>
@@ -10867,79 +10845,79 @@
         <v>17</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>283</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>285</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>289</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>291</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>294</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>295</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="R4" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="R4" s="26" t="s">
+      <c r="S4" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="S4" s="26" t="s">
+      <c r="T4" s="26" t="s">
         <v>299</v>
       </c>
-      <c r="T4" s="26" t="s">
+      <c r="U4" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="U4" s="26" t="s">
+      <c r="V4" s="26" t="s">
         <v>301</v>
       </c>
-      <c r="V4" s="26" t="s">
+      <c r="W4" s="26" t="s">
         <v>302</v>
       </c>
-      <c r="W4" s="26" t="s">
+      <c r="X4" s="26" t="s">
         <v>303</v>
       </c>
-      <c r="X4" s="26" t="s">
+      <c r="Y4" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="Y4" s="26" t="s">
+      <c r="Z4" s="26" t="s">
         <v>305</v>
-      </c>
-      <c r="Z4" s="26" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:26" s="18" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -10947,79 +10925,79 @@
         <v>33</v>
       </c>
       <c r="B5" s="26" t="s">
+        <v>306</v>
+      </c>
+      <c r="C5" s="26" t="s">
         <v>307</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="D5" s="26" t="s">
         <v>308</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="E5" s="26" t="s">
         <v>309</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="F5" s="26" t="s">
         <v>310</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="G5" s="26" t="s">
         <v>311</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="H5" s="26" t="s">
         <v>312</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="I5" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="I5" s="26" t="s">
+      <c r="J5" s="26" t="s">
         <v>314</v>
       </c>
-      <c r="J5" s="26" t="s">
+      <c r="K5" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="K5" s="26" t="s">
+      <c r="L5" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="L5" s="26" t="s">
+      <c r="M5" s="26" t="s">
         <v>317</v>
       </c>
-      <c r="M5" s="26" t="s">
+      <c r="N5" s="26" t="s">
         <v>318</v>
       </c>
-      <c r="N5" s="26" t="s">
+      <c r="O5" s="26" t="s">
         <v>319</v>
       </c>
-      <c r="O5" s="26" t="s">
+      <c r="P5" s="26" t="s">
         <v>320</v>
       </c>
-      <c r="P5" s="26" t="s">
+      <c r="Q5" s="26" t="s">
         <v>321</v>
       </c>
-      <c r="Q5" s="26" t="s">
+      <c r="R5" s="26" t="s">
         <v>322</v>
       </c>
-      <c r="R5" s="26" t="s">
+      <c r="S5" s="26" t="s">
         <v>323</v>
       </c>
-      <c r="S5" s="26" t="s">
+      <c r="T5" s="26" t="s">
         <v>324</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="U5" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="U5" s="26" t="s">
+      <c r="V5" s="26" t="s">
         <v>326</v>
       </c>
-      <c r="V5" s="26" t="s">
+      <c r="W5" s="26" t="s">
         <v>327</v>
       </c>
-      <c r="W5" s="26" t="s">
+      <c r="X5" s="26" t="s">
         <v>328</v>
       </c>
-      <c r="X5" s="26" t="s">
+      <c r="Y5" s="26" t="s">
         <v>329</v>
       </c>
-      <c r="Y5" s="26" t="s">
+      <c r="Z5" s="26" t="s">
         <v>330</v>
-      </c>
-      <c r="Z5" s="26" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="19.2" x14ac:dyDescent="0.3">
@@ -11686,58 +11664,58 @@
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>332</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="D3" s="26" t="s">
         <v>333</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>334</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>335</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>336</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>337</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="I3" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="J3" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="K3" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="L3" s="26" t="s">
         <v>341</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="M3" s="26" t="s">
         <v>342</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="N3" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="O3" s="26" t="s">
         <v>344</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="P3" s="26" t="s">
         <v>345</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="Q3" s="26" t="s">
         <v>346</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="R3" s="26" t="s">
         <v>347</v>
       </c>
-      <c r="R3" s="26" t="s">
+      <c r="S3" s="26" t="s">
         <v>348</v>
-      </c>
-      <c r="S3" s="26" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:19" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -11745,58 +11723,58 @@
         <v>33</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>349</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>350</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>351</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>352</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>353</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>354</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>355</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>356</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="26" t="s">
         <v>357</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="K4" s="26" t="s">
         <v>358</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>359</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>360</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="N4" s="26" t="s">
         <v>361</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>362</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>363</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="Q4" s="26" t="s">
         <v>364</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="R4" s="26" t="s">
         <v>365</v>
       </c>
-      <c r="R4" s="26" t="s">
+      <c r="S4" s="26" t="s">
         <v>366</v>
-      </c>
-      <c r="S4" s="26" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="19.2" x14ac:dyDescent="0.3">

--- a/Midterm_Grades.xlsx
+++ b/Midterm_Grades.xlsx
@@ -8,28 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saraa\OneDrive - Emirates Schools Establishment\Attachments\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E7411F-8774-4292-BB75-EA6447220CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D3A0E0-40A8-4590-90C6-5F0A83C613C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="1A" sheetId="1" r:id="rId1"/>
-    <sheet name="1B" sheetId="3" r:id="rId2"/>
-    <sheet name="2A" sheetId="4" r:id="rId3"/>
-    <sheet name="2B" sheetId="5" r:id="rId4"/>
-    <sheet name="3A" sheetId="6" r:id="rId5"/>
-    <sheet name="3B" sheetId="7" r:id="rId6"/>
-    <sheet name="4" sheetId="8" r:id="rId7"/>
-    <sheet name="5" sheetId="9" r:id="rId8"/>
-    <sheet name="6" sheetId="10" r:id="rId9"/>
-    <sheet name="7" sheetId="11" r:id="rId10"/>
-    <sheet name="8" sheetId="12" r:id="rId11"/>
-    <sheet name="9G" sheetId="13" r:id="rId12"/>
-    <sheet name="10A" sheetId="14" r:id="rId13"/>
-    <sheet name="10G" sheetId="15" r:id="rId14"/>
-    <sheet name="11G" sheetId="17" r:id="rId15"/>
-    <sheet name="12A" sheetId="18" r:id="rId16"/>
-    <sheet name="12G" sheetId="19" r:id="rId17"/>
+    <sheet name="11A" sheetId="20" r:id="rId1"/>
+    <sheet name="1A" sheetId="1" r:id="rId2"/>
+    <sheet name="1B" sheetId="3" r:id="rId3"/>
+    <sheet name="2A" sheetId="4" r:id="rId4"/>
+    <sheet name="2B" sheetId="5" r:id="rId5"/>
+    <sheet name="3A" sheetId="6" r:id="rId6"/>
+    <sheet name="3B" sheetId="7" r:id="rId7"/>
+    <sheet name="4" sheetId="8" r:id="rId8"/>
+    <sheet name="5" sheetId="9" r:id="rId9"/>
+    <sheet name="6" sheetId="10" r:id="rId10"/>
+    <sheet name="7" sheetId="11" r:id="rId11"/>
+    <sheet name="8" sheetId="12" r:id="rId12"/>
+    <sheet name="9G" sheetId="13" r:id="rId13"/>
+    <sheet name="10A" sheetId="14" r:id="rId14"/>
+    <sheet name="10G" sheetId="15" r:id="rId15"/>
+    <sheet name="11G" sheetId="17" r:id="rId16"/>
+    <sheet name="12A" sheetId="18" r:id="rId17"/>
+    <sheet name="12G" sheetId="19" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="542">
   <si>
     <t>Field</t>
   </si>
@@ -1675,6 +1676,9 @@
   </si>
   <si>
     <t>غبيشه ناصر مسلم محمد الخييلي</t>
+  </si>
+  <si>
+    <t>Mohammed Abdullah</t>
   </si>
 </sst>
 </file>
@@ -2402,22 +2406,128 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FFBAEFB-A5D4-428C-9885-E37F6BDBB7A5}">
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.6640625" style="13" customWidth="1"/>
-    <col min="2" max="16" width="23.88671875" style="13" customWidth="1"/>
-    <col min="17" max="16384" width="8.88671875" style="13"/>
+    <col min="2" max="2" width="23.88671875" style="13" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
+    </row>
+    <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="38">
+        <v>784000000000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="19.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="46"/>
+    </row>
+    <row r="6" spans="1:2" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A6" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="39">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A7" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="50">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A8" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="39">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A9" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="50">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A10" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="50">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A11" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="50">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:2" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:2" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:2" ht="14.4" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:S15"/>
+  <sheetFormatPr defaultColWidth="19.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="15" width="19.44140625" style="17"/>
+    <col min="16" max="17" width="19.44140625" style="22"/>
+    <col min="18" max="19" width="19.44140625" style="17"/>
+    <col min="20" max="16384" width="19.44140625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
@@ -2446,492 +2556,549 @@
         <v>10</v>
       </c>
       <c r="L1" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="26" t="s">
+      <c r="N1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="26" t="s">
+      <c r="O1" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="26" t="s">
+      <c r="P1" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="26" t="s">
+      <c r="Q1" s="26" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="58" t="s">
+      <c r="R1" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="S1" s="26" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="38">
-        <v>784201958584639</v>
+        <v>784201440695373</v>
       </c>
       <c r="C2" s="38">
-        <v>784202055785699</v>
+        <v>784201552809424</v>
       </c>
       <c r="D2" s="38">
-        <v>784201913274763</v>
+        <v>784201513704920</v>
       </c>
       <c r="E2" s="38">
-        <v>784202053694034</v>
+        <v>784201520202421</v>
       </c>
       <c r="F2" s="38">
-        <v>784201968373965</v>
+        <v>784201507072516</v>
       </c>
       <c r="G2" s="38">
-        <v>784201991724903</v>
+        <v>784201570864815</v>
       </c>
       <c r="H2" s="38">
-        <v>784201942428273</v>
+        <v>784201547250684</v>
       </c>
       <c r="I2" s="38">
-        <v>784202031323201</v>
+        <v>784201529602928</v>
       </c>
       <c r="J2" s="38">
-        <v>784201975394624</v>
+        <v>784201542647173</v>
       </c>
       <c r="K2" s="38">
-        <v>784202080737632</v>
+        <v>784201597141577</v>
       </c>
       <c r="L2" s="38">
-        <v>784202071079143</v>
+        <v>784201575846270</v>
       </c>
       <c r="M2" s="38">
-        <v>784202095015677</v>
+        <v>784201550690495</v>
       </c>
       <c r="N2" s="38">
-        <v>784201927258141</v>
+        <v>784201539106373</v>
       </c>
       <c r="O2" s="38">
-        <v>784201902959184</v>
+        <v>784201583294869</v>
       </c>
       <c r="P2" s="38">
-        <v>784202035919152</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="14" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="58" t="s">
+        <v>784201571054689</v>
+      </c>
+      <c r="Q2" s="38">
+        <v>784201575170366</v>
+      </c>
+      <c r="R2" s="38">
+        <v>784201593763747</v>
+      </c>
+      <c r="S2" s="38">
+        <v>784201574939159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>18</v>
+        <v>331</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>21</v>
+        <v>334</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>22</v>
+        <v>335</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>23</v>
+        <v>336</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>24</v>
+        <v>337</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="85" t="s">
-        <v>26</v>
+        <v>338</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>339</v>
       </c>
       <c r="K3" s="26" t="s">
-        <v>27</v>
+        <v>340</v>
       </c>
       <c r="L3" s="26" t="s">
-        <v>28</v>
+        <v>341</v>
       </c>
       <c r="M3" s="26" t="s">
-        <v>29</v>
+        <v>342</v>
       </c>
       <c r="N3" s="26" t="s">
-        <v>30</v>
+        <v>343</v>
       </c>
       <c r="O3" s="26" t="s">
-        <v>31</v>
+        <v>344</v>
       </c>
       <c r="P3" s="26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="58" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q3" s="26" t="s">
+        <v>346</v>
+      </c>
+      <c r="R3" s="26" t="s">
+        <v>347</v>
+      </c>
+      <c r="S3" s="26" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="26" t="s">
         <v>33</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>34</v>
+        <v>349</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>35</v>
+        <v>350</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>36</v>
+        <v>351</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>37</v>
+        <v>352</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>39</v>
+        <v>354</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>40</v>
+        <v>355</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>41</v>
+        <v>356</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>42</v>
+        <v>357</v>
       </c>
       <c r="K4" s="26" t="s">
-        <v>43</v>
+        <v>358</v>
       </c>
       <c r="L4" s="26" t="s">
-        <v>44</v>
+        <v>359</v>
       </c>
       <c r="M4" s="26" t="s">
-        <v>45</v>
+        <v>360</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>46</v>
+        <v>361</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>47</v>
+        <v>362</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="19.2" x14ac:dyDescent="0.3">
+        <v>363</v>
+      </c>
+      <c r="Q4" s="26" t="s">
+        <v>364</v>
+      </c>
+      <c r="R4" s="26" t="s">
+        <v>365</v>
+      </c>
+      <c r="S4" s="26" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-    </row>
-    <row r="6" spans="1:16" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="45"/>
+      <c r="S5" s="45"/>
+    </row>
+    <row r="6" spans="1:19" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>50</v>
       </c>
       <c r="B6" s="39">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="C6" s="39">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D6" s="39">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E6" s="39">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="F6" s="39">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G6" s="39">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="H6" s="39">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I6" s="39">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J6" s="39">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="K6" s="39">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="L6" s="39">
+        <v>60</v>
+      </c>
+      <c r="M6" s="39">
+        <v>75</v>
+      </c>
+      <c r="N6" s="39">
+        <v>80</v>
+      </c>
+      <c r="O6" s="39">
+        <v>80</v>
+      </c>
+      <c r="P6" s="56">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="56">
+        <v>88</v>
+      </c>
+      <c r="R6" s="39">
+        <v>80</v>
+      </c>
+      <c r="S6" s="39">
         <v>65</v>
       </c>
-      <c r="M6" s="39">
-        <v>50</v>
-      </c>
-      <c r="N6" s="39">
-        <v>70</v>
-      </c>
-      <c r="O6" s="39">
-        <v>80</v>
-      </c>
-      <c r="P6" s="39">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="s">
         <v>51</v>
       </c>
       <c r="B7" s="50">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C7" s="50">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D7" s="50">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E7" s="50">
+        <v>70</v>
+      </c>
+      <c r="F7" s="50">
+        <v>40</v>
+      </c>
+      <c r="G7" s="50">
+        <v>80</v>
+      </c>
+      <c r="H7" s="50">
+        <v>70</v>
+      </c>
+      <c r="I7" s="50">
+        <v>40</v>
+      </c>
+      <c r="J7" s="50">
+        <v>40</v>
+      </c>
+      <c r="K7" s="50">
+        <v>50</v>
+      </c>
+      <c r="L7" s="50">
+        <v>50</v>
+      </c>
+      <c r="M7" s="50">
         <v>60</v>
       </c>
-      <c r="F7" s="50">
-        <v>70</v>
-      </c>
-      <c r="G7" s="50">
-        <v>70</v>
-      </c>
-      <c r="H7" s="50">
-        <v>90</v>
-      </c>
-      <c r="I7" s="50">
-        <v>70</v>
-      </c>
-      <c r="J7" s="50">
+      <c r="N7" s="50">
+        <v>50</v>
+      </c>
+      <c r="O7" s="50">
+        <v>20</v>
+      </c>
+      <c r="P7" s="57">
+        <v>40</v>
+      </c>
+      <c r="Q7" s="57">
         <v>60</v>
       </c>
-      <c r="K7" s="50">
-        <v>90</v>
-      </c>
-      <c r="L7" s="50">
-        <v>80</v>
-      </c>
-      <c r="M7" s="50">
-        <v>70</v>
-      </c>
-      <c r="N7" s="50">
-        <v>80</v>
-      </c>
-      <c r="O7" s="50">
-        <v>90</v>
-      </c>
-      <c r="P7" s="50">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="R7" s="37">
+        <v>40</v>
+      </c>
+      <c r="S7" s="37">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="39">
-        <v>60</v>
-      </c>
-      <c r="C8" s="39">
-        <v>85</v>
-      </c>
-      <c r="D8" s="39">
-        <v>60</v>
-      </c>
-      <c r="E8" s="39">
-        <v>58</v>
-      </c>
-      <c r="F8" s="39">
-        <v>60</v>
-      </c>
-      <c r="G8" s="39">
-        <v>60</v>
-      </c>
-      <c r="H8" s="39">
-        <v>85</v>
-      </c>
-      <c r="I8" s="39">
-        <v>55</v>
-      </c>
-      <c r="J8" s="39">
-        <v>50</v>
-      </c>
-      <c r="K8" s="39">
-        <v>88</v>
-      </c>
-      <c r="L8" s="39">
-        <v>70</v>
-      </c>
-      <c r="M8" s="39">
-        <v>60</v>
-      </c>
-      <c r="N8" s="39">
-        <v>72</v>
-      </c>
-      <c r="O8" s="39">
-        <v>85</v>
-      </c>
-      <c r="P8" s="39">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="56"/>
+      <c r="Q8" s="56"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="39"/>
+    </row>
+    <row r="9" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="s">
         <v>53</v>
       </c>
       <c r="B9" s="50">
+        <v>73</v>
+      </c>
+      <c r="C9" s="50">
+        <v>43</v>
+      </c>
+      <c r="D9" s="50">
+        <v>54</v>
+      </c>
+      <c r="E9" s="50">
+        <v>77</v>
+      </c>
+      <c r="F9" s="50">
         <v>35</v>
       </c>
-      <c r="C9" s="50">
-        <v>65</v>
-      </c>
-      <c r="D9" s="50">
-        <v>50</v>
-      </c>
-      <c r="E9" s="50">
-        <v>50</v>
-      </c>
-      <c r="F9" s="50">
-        <v>45</v>
-      </c>
       <c r="G9" s="50">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="H9" s="50">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I9" s="50">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="J9" s="50">
+        <v>88</v>
+      </c>
+      <c r="K9" s="50">
+        <v>71</v>
+      </c>
+      <c r="L9" s="50">
+        <v>54</v>
+      </c>
+      <c r="M9" s="50">
+        <v>67</v>
+      </c>
+      <c r="N9" s="50">
+        <v>69</v>
+      </c>
+      <c r="O9" s="50">
+        <v>75</v>
+      </c>
+      <c r="P9" s="57">
         <v>40</v>
       </c>
-      <c r="K9" s="50">
-        <v>68</v>
-      </c>
-      <c r="L9" s="50">
-        <v>60</v>
-      </c>
-      <c r="M9" s="50">
-        <v>55</v>
-      </c>
-      <c r="N9" s="50">
-        <v>75</v>
-      </c>
-      <c r="O9" s="50">
-        <v>65</v>
-      </c>
-      <c r="P9" s="50">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="Q9" s="57">
+        <v>81</v>
+      </c>
+      <c r="R9" s="37">
+        <v>71</v>
+      </c>
+      <c r="S9" s="37">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="50">
+      <c r="B10" s="39">
         <v>45</v>
       </c>
-      <c r="C10" s="50">
-        <v>70</v>
-      </c>
-      <c r="D10" s="50">
+      <c r="C10" s="39">
+        <v>52</v>
+      </c>
+      <c r="D10" s="39">
         <v>50</v>
       </c>
-      <c r="E10" s="50">
+      <c r="E10" s="39">
+        <v>60</v>
+      </c>
+      <c r="F10" s="39">
+        <v>40</v>
+      </c>
+      <c r="G10" s="39">
+        <v>65</v>
+      </c>
+      <c r="H10" s="39">
+        <v>53</v>
+      </c>
+      <c r="I10" s="39">
+        <v>60</v>
+      </c>
+      <c r="J10" s="39">
+        <v>70</v>
+      </c>
+      <c r="K10" s="39">
+        <v>60</v>
+      </c>
+      <c r="L10" s="39">
+        <v>48</v>
+      </c>
+      <c r="M10" s="39">
+        <v>64</v>
+      </c>
+      <c r="N10" s="39">
         <v>50</v>
       </c>
-      <c r="F10" s="50">
-        <v>45</v>
-      </c>
-      <c r="G10" s="50">
-        <v>30</v>
-      </c>
-      <c r="H10" s="50">
-        <v>70</v>
-      </c>
-      <c r="I10" s="50">
-        <v>50</v>
-      </c>
-      <c r="J10" s="50">
-        <v>40</v>
-      </c>
-      <c r="K10" s="50">
-        <v>70</v>
-      </c>
-      <c r="L10" s="50">
-        <v>60</v>
-      </c>
-      <c r="M10" s="50">
-        <v>50</v>
-      </c>
-      <c r="N10" s="50">
-        <v>80</v>
-      </c>
-      <c r="O10" s="50">
-        <v>65</v>
-      </c>
-      <c r="P10" s="50">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="O10" s="39">
+        <v>52</v>
+      </c>
+      <c r="P10" s="56">
+        <v>37</v>
+      </c>
+      <c r="Q10" s="56">
+        <v>68</v>
+      </c>
+      <c r="R10" s="39">
+        <v>52</v>
+      </c>
+      <c r="S10" s="39">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="49" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="50">
+        <v>30</v>
+      </c>
+      <c r="C11" s="50">
+        <v>50</v>
+      </c>
+      <c r="D11" s="50">
+        <v>50</v>
+      </c>
+      <c r="E11" s="50">
         <v>35</v>
-      </c>
-      <c r="C11" s="50">
-        <v>70</v>
-      </c>
-      <c r="D11" s="50">
-        <v>55</v>
-      </c>
-      <c r="E11" s="50">
-        <v>45</v>
       </c>
       <c r="F11" s="50">
         <v>40</v>
       </c>
       <c r="G11" s="50">
+        <v>75</v>
+      </c>
+      <c r="H11" s="50">
         <v>35</v>
       </c>
-      <c r="H11" s="50">
-        <v>70</v>
-      </c>
       <c r="I11" s="50">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J11" s="50">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K11" s="50">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="L11" s="50">
+        <v>55</v>
+      </c>
+      <c r="M11" s="50">
+        <v>75</v>
+      </c>
+      <c r="N11" s="50">
+        <v>35</v>
+      </c>
+      <c r="O11" s="50">
+        <v>35</v>
+      </c>
+      <c r="P11" s="57">
+        <v>50</v>
+      </c>
+      <c r="Q11" s="57">
         <v>65</v>
       </c>
-      <c r="M11" s="50">
-        <v>58</v>
-      </c>
-      <c r="N11" s="50">
-        <v>78</v>
-      </c>
-      <c r="O11" s="50">
+      <c r="R11" s="37">
         <v>65</v>
       </c>
-      <c r="P11" s="50">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="S11" s="37">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
@@ -2946,8 +3113,11 @@
       <c r="N12"/>
       <c r="O12"/>
       <c r="P12"/>
-    </row>
-    <row r="13" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q12"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
@@ -2962,8 +3132,11 @@
       <c r="N13"/>
       <c r="O13"/>
       <c r="P13"/>
-    </row>
-    <row r="14" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q13"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -2978,8 +3151,11 @@
       <c r="N14"/>
       <c r="O14"/>
       <c r="P14"/>
-    </row>
-    <row r="15" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q14"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
@@ -2994,13 +3170,16 @@
       <c r="N15"/>
       <c r="O15"/>
       <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3608,7 +3787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:U15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4336,7 +4515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:R15"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5021,7 +5200,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5199,7 +5378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -5675,7 +5854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6164,7 +6343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -6425,7 +6604,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6567,6 +6746,605 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.6640625" style="13" customWidth="1"/>
+    <col min="2" max="16" width="23.88671875" style="13" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="38">
+        <v>784201958584639</v>
+      </c>
+      <c r="C2" s="38">
+        <v>784202055785699</v>
+      </c>
+      <c r="D2" s="38">
+        <v>784201913274763</v>
+      </c>
+      <c r="E2" s="38">
+        <v>784202053694034</v>
+      </c>
+      <c r="F2" s="38">
+        <v>784201968373965</v>
+      </c>
+      <c r="G2" s="38">
+        <v>784201991724903</v>
+      </c>
+      <c r="H2" s="38">
+        <v>784201942428273</v>
+      </c>
+      <c r="I2" s="38">
+        <v>784202031323201</v>
+      </c>
+      <c r="J2" s="38">
+        <v>784201975394624</v>
+      </c>
+      <c r="K2" s="38">
+        <v>784202080737632</v>
+      </c>
+      <c r="L2" s="38">
+        <v>784202071079143</v>
+      </c>
+      <c r="M2" s="38">
+        <v>784202095015677</v>
+      </c>
+      <c r="N2" s="38">
+        <v>784201927258141</v>
+      </c>
+      <c r="O2" s="38">
+        <v>784201902959184</v>
+      </c>
+      <c r="P2" s="38">
+        <v>784202035919152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="14" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="85" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="19.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+    </row>
+    <row r="6" spans="1:16" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A6" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="39">
+        <v>56</v>
+      </c>
+      <c r="C6" s="39">
+        <v>80</v>
+      </c>
+      <c r="D6" s="39">
+        <v>55</v>
+      </c>
+      <c r="E6" s="39">
+        <v>55</v>
+      </c>
+      <c r="F6" s="39">
+        <v>45</v>
+      </c>
+      <c r="G6" s="39">
+        <v>40</v>
+      </c>
+      <c r="H6" s="39">
+        <v>80</v>
+      </c>
+      <c r="I6" s="39">
+        <v>45</v>
+      </c>
+      <c r="J6" s="39">
+        <v>45</v>
+      </c>
+      <c r="K6" s="39">
+        <v>80</v>
+      </c>
+      <c r="L6" s="39">
+        <v>65</v>
+      </c>
+      <c r="M6" s="39">
+        <v>50</v>
+      </c>
+      <c r="N6" s="39">
+        <v>70</v>
+      </c>
+      <c r="O6" s="39">
+        <v>80</v>
+      </c>
+      <c r="P6" s="39">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="A7" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="50">
+        <v>70</v>
+      </c>
+      <c r="C7" s="50">
+        <v>90</v>
+      </c>
+      <c r="D7" s="50">
+        <v>70</v>
+      </c>
+      <c r="E7" s="50">
+        <v>60</v>
+      </c>
+      <c r="F7" s="50">
+        <v>70</v>
+      </c>
+      <c r="G7" s="50">
+        <v>70</v>
+      </c>
+      <c r="H7" s="50">
+        <v>90</v>
+      </c>
+      <c r="I7" s="50">
+        <v>70</v>
+      </c>
+      <c r="J7" s="50">
+        <v>60</v>
+      </c>
+      <c r="K7" s="50">
+        <v>90</v>
+      </c>
+      <c r="L7" s="50">
+        <v>80</v>
+      </c>
+      <c r="M7" s="50">
+        <v>70</v>
+      </c>
+      <c r="N7" s="50">
+        <v>80</v>
+      </c>
+      <c r="O7" s="50">
+        <v>90</v>
+      </c>
+      <c r="P7" s="50">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A8" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="39">
+        <v>60</v>
+      </c>
+      <c r="C8" s="39">
+        <v>85</v>
+      </c>
+      <c r="D8" s="39">
+        <v>60</v>
+      </c>
+      <c r="E8" s="39">
+        <v>58</v>
+      </c>
+      <c r="F8" s="39">
+        <v>60</v>
+      </c>
+      <c r="G8" s="39">
+        <v>60</v>
+      </c>
+      <c r="H8" s="39">
+        <v>85</v>
+      </c>
+      <c r="I8" s="39">
+        <v>55</v>
+      </c>
+      <c r="J8" s="39">
+        <v>50</v>
+      </c>
+      <c r="K8" s="39">
+        <v>88</v>
+      </c>
+      <c r="L8" s="39">
+        <v>70</v>
+      </c>
+      <c r="M8" s="39">
+        <v>60</v>
+      </c>
+      <c r="N8" s="39">
+        <v>72</v>
+      </c>
+      <c r="O8" s="39">
+        <v>85</v>
+      </c>
+      <c r="P8" s="39">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="A9" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="50">
+        <v>35</v>
+      </c>
+      <c r="C9" s="50">
+        <v>65</v>
+      </c>
+      <c r="D9" s="50">
+        <v>50</v>
+      </c>
+      <c r="E9" s="50">
+        <v>50</v>
+      </c>
+      <c r="F9" s="50">
+        <v>45</v>
+      </c>
+      <c r="G9" s="50">
+        <v>30</v>
+      </c>
+      <c r="H9" s="50">
+        <v>70</v>
+      </c>
+      <c r="I9" s="50">
+        <v>60</v>
+      </c>
+      <c r="J9" s="50">
+        <v>40</v>
+      </c>
+      <c r="K9" s="50">
+        <v>68</v>
+      </c>
+      <c r="L9" s="50">
+        <v>60</v>
+      </c>
+      <c r="M9" s="50">
+        <v>55</v>
+      </c>
+      <c r="N9" s="50">
+        <v>75</v>
+      </c>
+      <c r="O9" s="50">
+        <v>65</v>
+      </c>
+      <c r="P9" s="50">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A10" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="50">
+        <v>45</v>
+      </c>
+      <c r="C10" s="50">
+        <v>70</v>
+      </c>
+      <c r="D10" s="50">
+        <v>50</v>
+      </c>
+      <c r="E10" s="50">
+        <v>50</v>
+      </c>
+      <c r="F10" s="50">
+        <v>45</v>
+      </c>
+      <c r="G10" s="50">
+        <v>30</v>
+      </c>
+      <c r="H10" s="50">
+        <v>70</v>
+      </c>
+      <c r="I10" s="50">
+        <v>50</v>
+      </c>
+      <c r="J10" s="50">
+        <v>40</v>
+      </c>
+      <c r="K10" s="50">
+        <v>70</v>
+      </c>
+      <c r="L10" s="50">
+        <v>60</v>
+      </c>
+      <c r="M10" s="50">
+        <v>50</v>
+      </c>
+      <c r="N10" s="50">
+        <v>80</v>
+      </c>
+      <c r="O10" s="50">
+        <v>65</v>
+      </c>
+      <c r="P10" s="50">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="A11" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="50">
+        <v>35</v>
+      </c>
+      <c r="C11" s="50">
+        <v>70</v>
+      </c>
+      <c r="D11" s="50">
+        <v>55</v>
+      </c>
+      <c r="E11" s="50">
+        <v>45</v>
+      </c>
+      <c r="F11" s="50">
+        <v>40</v>
+      </c>
+      <c r="G11" s="50">
+        <v>35</v>
+      </c>
+      <c r="H11" s="50">
+        <v>70</v>
+      </c>
+      <c r="I11" s="50">
+        <v>60</v>
+      </c>
+      <c r="J11" s="50">
+        <v>40</v>
+      </c>
+      <c r="K11" s="50">
+        <v>68</v>
+      </c>
+      <c r="L11" s="50">
+        <v>65</v>
+      </c>
+      <c r="M11" s="50">
+        <v>58</v>
+      </c>
+      <c r="N11" s="50">
+        <v>78</v>
+      </c>
+      <c r="O11" s="50">
+        <v>65</v>
+      </c>
+      <c r="P11" s="50">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+    </row>
+    <row r="13" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
+    </row>
+    <row r="14" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+    </row>
+    <row r="15" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7201,7 +7979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S15"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7882,7 +8660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:R15"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8533,7 +9311,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9244,7 +10022,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:T15"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9923,7 +10701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:R17"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10566,7 +11344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:Z15"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11528,673 +12306,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:S15"/>
-  <sheetFormatPr defaultColWidth="19.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="15" width="19.44140625" style="17"/>
-    <col min="16" max="17" width="19.44140625" style="22"/>
-    <col min="18" max="19" width="19.44140625" style="17"/>
-    <col min="20" max="16384" width="19.44140625" style="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="M1" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="S1" s="26" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="38">
-        <v>784201440695373</v>
-      </c>
-      <c r="C2" s="38">
-        <v>784201552809424</v>
-      </c>
-      <c r="D2" s="38">
-        <v>784201513704920</v>
-      </c>
-      <c r="E2" s="38">
-        <v>784201520202421</v>
-      </c>
-      <c r="F2" s="38">
-        <v>784201507072516</v>
-      </c>
-      <c r="G2" s="38">
-        <v>784201570864815</v>
-      </c>
-      <c r="H2" s="38">
-        <v>784201547250684</v>
-      </c>
-      <c r="I2" s="38">
-        <v>784201529602928</v>
-      </c>
-      <c r="J2" s="38">
-        <v>784201542647173</v>
-      </c>
-      <c r="K2" s="38">
-        <v>784201597141577</v>
-      </c>
-      <c r="L2" s="38">
-        <v>784201575846270</v>
-      </c>
-      <c r="M2" s="38">
-        <v>784201550690495</v>
-      </c>
-      <c r="N2" s="38">
-        <v>784201539106373</v>
-      </c>
-      <c r="O2" s="38">
-        <v>784201583294869</v>
-      </c>
-      <c r="P2" s="38">
-        <v>784201571054689</v>
-      </c>
-      <c r="Q2" s="38">
-        <v>784201575170366</v>
-      </c>
-      <c r="R2" s="38">
-        <v>784201593763747</v>
-      </c>
-      <c r="S2" s="38">
-        <v>784201574939159</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>332</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>333</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>336</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>337</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>338</v>
-      </c>
-      <c r="J3" s="26" t="s">
-        <v>339</v>
-      </c>
-      <c r="K3" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="L3" s="26" t="s">
-        <v>341</v>
-      </c>
-      <c r="M3" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="N3" s="26" t="s">
-        <v>343</v>
-      </c>
-      <c r="O3" s="26" t="s">
-        <v>344</v>
-      </c>
-      <c r="P3" s="26" t="s">
-        <v>345</v>
-      </c>
-      <c r="Q3" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="R3" s="26" t="s">
-        <v>347</v>
-      </c>
-      <c r="S3" s="26" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>349</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>350</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>351</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>352</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>353</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>354</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>355</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>356</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>357</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>358</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>359</v>
-      </c>
-      <c r="M4" s="26" t="s">
-        <v>360</v>
-      </c>
-      <c r="N4" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="O4" s="26" t="s">
-        <v>362</v>
-      </c>
-      <c r="P4" s="26" t="s">
-        <v>363</v>
-      </c>
-      <c r="Q4" s="26" t="s">
-        <v>364</v>
-      </c>
-      <c r="R4" s="26" t="s">
-        <v>365</v>
-      </c>
-      <c r="S4" s="26" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-    </row>
-    <row r="6" spans="1:19" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A6" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="39">
-        <v>90</v>
-      </c>
-      <c r="C6" s="39">
-        <v>68</v>
-      </c>
-      <c r="D6" s="39">
-        <v>65</v>
-      </c>
-      <c r="E6" s="39">
-        <v>90</v>
-      </c>
-      <c r="F6" s="39">
-        <v>40</v>
-      </c>
-      <c r="G6" s="39">
-        <v>88</v>
-      </c>
-      <c r="H6" s="39">
-        <v>90</v>
-      </c>
-      <c r="I6" s="39">
-        <v>60</v>
-      </c>
-      <c r="J6" s="39">
-        <v>70</v>
-      </c>
-      <c r="K6" s="39">
-        <v>88</v>
-      </c>
-      <c r="L6" s="39">
-        <v>60</v>
-      </c>
-      <c r="M6" s="39">
-        <v>75</v>
-      </c>
-      <c r="N6" s="39">
-        <v>80</v>
-      </c>
-      <c r="O6" s="39">
-        <v>80</v>
-      </c>
-      <c r="P6" s="56">
-        <v>20</v>
-      </c>
-      <c r="Q6" s="56">
-        <v>88</v>
-      </c>
-      <c r="R6" s="39">
-        <v>80</v>
-      </c>
-      <c r="S6" s="39">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="18" x14ac:dyDescent="0.3">
-      <c r="A7" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="50">
-        <v>100</v>
-      </c>
-      <c r="C7" s="50">
-        <v>60</v>
-      </c>
-      <c r="D7" s="50">
-        <v>60</v>
-      </c>
-      <c r="E7" s="50">
-        <v>70</v>
-      </c>
-      <c r="F7" s="50">
-        <v>40</v>
-      </c>
-      <c r="G7" s="50">
-        <v>80</v>
-      </c>
-      <c r="H7" s="50">
-        <v>70</v>
-      </c>
-      <c r="I7" s="50">
-        <v>40</v>
-      </c>
-      <c r="J7" s="50">
-        <v>40</v>
-      </c>
-      <c r="K7" s="50">
-        <v>50</v>
-      </c>
-      <c r="L7" s="50">
-        <v>50</v>
-      </c>
-      <c r="M7" s="50">
-        <v>60</v>
-      </c>
-      <c r="N7" s="50">
-        <v>50</v>
-      </c>
-      <c r="O7" s="50">
-        <v>20</v>
-      </c>
-      <c r="P7" s="57">
-        <v>40</v>
-      </c>
-      <c r="Q7" s="57">
-        <v>60</v>
-      </c>
-      <c r="R7" s="37">
-        <v>40</v>
-      </c>
-      <c r="S7" s="37">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A8" s="47" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="56"/>
-      <c r="Q8" s="56"/>
-      <c r="R8" s="39"/>
-      <c r="S8" s="39"/>
-    </row>
-    <row r="9" spans="1:19" ht="18" x14ac:dyDescent="0.3">
-      <c r="A9" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="50">
-        <v>73</v>
-      </c>
-      <c r="C9" s="50">
-        <v>43</v>
-      </c>
-      <c r="D9" s="50">
-        <v>54</v>
-      </c>
-      <c r="E9" s="50">
-        <v>77</v>
-      </c>
-      <c r="F9" s="50">
-        <v>35</v>
-      </c>
-      <c r="G9" s="50">
-        <v>91</v>
-      </c>
-      <c r="H9" s="50">
-        <v>67</v>
-      </c>
-      <c r="I9" s="50">
-        <v>74</v>
-      </c>
-      <c r="J9" s="50">
-        <v>88</v>
-      </c>
-      <c r="K9" s="50">
-        <v>71</v>
-      </c>
-      <c r="L9" s="50">
-        <v>54</v>
-      </c>
-      <c r="M9" s="50">
-        <v>67</v>
-      </c>
-      <c r="N9" s="50">
-        <v>69</v>
-      </c>
-      <c r="O9" s="50">
-        <v>75</v>
-      </c>
-      <c r="P9" s="57">
-        <v>40</v>
-      </c>
-      <c r="Q9" s="57">
-        <v>81</v>
-      </c>
-      <c r="R9" s="37">
-        <v>71</v>
-      </c>
-      <c r="S9" s="37">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A10" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="39">
-        <v>45</v>
-      </c>
-      <c r="C10" s="39">
-        <v>52</v>
-      </c>
-      <c r="D10" s="39">
-        <v>50</v>
-      </c>
-      <c r="E10" s="39">
-        <v>60</v>
-      </c>
-      <c r="F10" s="39">
-        <v>40</v>
-      </c>
-      <c r="G10" s="39">
-        <v>65</v>
-      </c>
-      <c r="H10" s="39">
-        <v>53</v>
-      </c>
-      <c r="I10" s="39">
-        <v>60</v>
-      </c>
-      <c r="J10" s="39">
-        <v>70</v>
-      </c>
-      <c r="K10" s="39">
-        <v>60</v>
-      </c>
-      <c r="L10" s="39">
-        <v>48</v>
-      </c>
-      <c r="M10" s="39">
-        <v>64</v>
-      </c>
-      <c r="N10" s="39">
-        <v>50</v>
-      </c>
-      <c r="O10" s="39">
-        <v>52</v>
-      </c>
-      <c r="P10" s="56">
-        <v>37</v>
-      </c>
-      <c r="Q10" s="56">
-        <v>68</v>
-      </c>
-      <c r="R10" s="39">
-        <v>52</v>
-      </c>
-      <c r="S10" s="39">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="18" x14ac:dyDescent="0.3">
-      <c r="A11" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="50">
-        <v>30</v>
-      </c>
-      <c r="C11" s="50">
-        <v>50</v>
-      </c>
-      <c r="D11" s="50">
-        <v>50</v>
-      </c>
-      <c r="E11" s="50">
-        <v>35</v>
-      </c>
-      <c r="F11" s="50">
-        <v>40</v>
-      </c>
-      <c r="G11" s="50">
-        <v>75</v>
-      </c>
-      <c r="H11" s="50">
-        <v>35</v>
-      </c>
-      <c r="I11" s="50">
-        <v>55</v>
-      </c>
-      <c r="J11" s="50">
-        <v>55</v>
-      </c>
-      <c r="K11" s="50">
-        <v>45</v>
-      </c>
-      <c r="L11" s="50">
-        <v>55</v>
-      </c>
-      <c r="M11" s="50">
-        <v>75</v>
-      </c>
-      <c r="N11" s="50">
-        <v>35</v>
-      </c>
-      <c r="O11" s="50">
-        <v>35</v>
-      </c>
-      <c r="P11" s="57">
-        <v>50</v>
-      </c>
-      <c r="Q11" s="57">
-        <v>65</v>
-      </c>
-      <c r="R11" s="37">
-        <v>65</v>
-      </c>
-      <c r="S11" s="37">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-      <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12"/>
-      <c r="N12"/>
-      <c r="O12"/>
-      <c r="P12"/>
-      <c r="Q12"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
-      <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13"/>
-      <c r="N13"/>
-      <c r="O13"/>
-      <c r="P13"/>
-      <c r="Q13"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-      <c r="K14"/>
-      <c r="L14"/>
-      <c r="M14"/>
-      <c r="N14"/>
-      <c r="O14"/>
-      <c r="P14"/>
-      <c r="Q14"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15"/>
-      <c r="P15"/>
-      <c r="Q15"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>